--- a/AAII_Financials/Yearly/KAOOY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/KAOOY_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="92">
   <si>
     <t>KAOOY</t>
   </si>
@@ -656,136 +656,148 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>3</v>
+      <c r="I7" s="2">
+        <v>43465</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K7" s="2"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L7" s="2"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>10299000</v>
+        <v>10329600</v>
       </c>
       <c r="E8" s="3">
-        <v>9420600</v>
+        <v>10454100</v>
       </c>
       <c r="F8" s="3">
-        <v>9176500</v>
+        <v>9562500</v>
       </c>
       <c r="G8" s="3">
-        <v>9974900</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
+        <v>9314700</v>
+      </c>
+      <c r="H8" s="3">
+        <v>10125100</v>
+      </c>
+      <c r="I8" s="3">
+        <v>10164000</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K8" s="3"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L8" s="3"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>6658000</v>
+        <v>6552300</v>
       </c>
       <c r="E9" s="3">
-        <v>5614600</v>
+        <v>6758300</v>
       </c>
       <c r="F9" s="3">
-        <v>5254300</v>
+        <v>5699200</v>
       </c>
       <c r="G9" s="3">
-        <v>5635500</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
+        <v>5333400</v>
+      </c>
+      <c r="H9" s="3">
+        <v>5720400</v>
+      </c>
+      <c r="I9" s="3">
+        <v>5755900</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K9" s="3"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L9" s="3"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>3641000</v>
+        <v>3777300</v>
       </c>
       <c r="E10" s="3">
-        <v>3806000</v>
+        <v>3695800</v>
       </c>
       <c r="F10" s="3">
-        <v>3922200</v>
+        <v>3863300</v>
       </c>
       <c r="G10" s="3">
-        <v>4339400</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
+        <v>3981300</v>
+      </c>
+      <c r="H10" s="3">
+        <v>4404700</v>
+      </c>
+      <c r="I10" s="3">
+        <v>4408100</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K10" s="3"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L10" s="3"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -797,35 +809,39 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>402400</v>
+        <v>421800</v>
       </c>
       <c r="E12" s="3">
-        <v>391700</v>
+        <v>408500</v>
       </c>
       <c r="F12" s="3">
-        <v>388500</v>
+        <v>397600</v>
       </c>
       <c r="G12" s="3">
-        <v>392700</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>3</v>
+        <v>394400</v>
+      </c>
+      <c r="H12" s="3">
+        <v>398600</v>
+      </c>
+      <c r="I12" s="3">
+        <v>388700</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K12" s="3"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L12" s="3"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -850,63 +866,72 @@
       <c r="J13" s="3">
         <v>0</v>
       </c>
-      <c r="K13" s="3"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K13" s="3">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
         <v>200</v>
       </c>
-      <c r="E14" s="3">
-        <v>30200</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3">
-        <v>5000</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
+      <c r="F14" s="3">
+        <v>30700</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
+        <v>5100</v>
+      </c>
+      <c r="I14" s="3">
+        <v>10200</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>176000</v>
+        <v>187500</v>
       </c>
       <c r="E15" s="3">
-        <v>173900</v>
+        <v>178600</v>
       </c>
       <c r="F15" s="3">
-        <v>180700</v>
+        <v>176500</v>
       </c>
       <c r="G15" s="3">
-        <v>177500</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>3</v>
+        <v>183400</v>
+      </c>
+      <c r="H15" s="3">
+        <v>180100</v>
+      </c>
+      <c r="I15" s="3">
+        <v>108200</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K15" s="3"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L15" s="3"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -915,62 +940,69 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>9568200</v>
+        <v>9924900</v>
       </c>
       <c r="E17" s="3">
-        <v>8467700</v>
+        <v>9712300</v>
       </c>
       <c r="F17" s="3">
-        <v>8010700</v>
+        <v>8595200</v>
       </c>
       <c r="G17" s="3">
-        <v>8569000</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>3</v>
+        <v>8131400</v>
+      </c>
+      <c r="H17" s="3">
+        <v>8698100</v>
+      </c>
+      <c r="I17" s="3">
+        <v>8764000</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K17" s="3"/>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L17" s="3"/>
+    </row>
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>730900</v>
+        <v>404600</v>
       </c>
       <c r="E18" s="3">
-        <v>952900</v>
+        <v>741900</v>
       </c>
       <c r="F18" s="3">
-        <v>1165700</v>
+        <v>967300</v>
       </c>
       <c r="G18" s="3">
-        <v>1405800</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
+        <v>1183300</v>
+      </c>
+      <c r="H18" s="3">
+        <v>1427000</v>
+      </c>
+      <c r="I18" s="3">
+        <v>1399900</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K18" s="3"/>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L18" s="3"/>
+    </row>
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -982,52 +1014,56 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>54000</v>
+        <v>25700</v>
       </c>
       <c r="E20" s="3">
-        <v>59600</v>
+        <v>54800</v>
       </c>
       <c r="F20" s="3">
-        <v>17500</v>
+        <v>60500</v>
       </c>
       <c r="G20" s="3">
-        <v>17200</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
+        <v>17700</v>
+      </c>
+      <c r="H20" s="3">
+        <v>17400</v>
+      </c>
+      <c r="I20" s="3">
+        <v>9900</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K20" s="3"/>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L20" s="3"/>
+    </row>
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1378000</v>
+        <v>1036900</v>
       </c>
       <c r="E21" s="3">
-        <v>1589900</v>
+        <v>1404200</v>
       </c>
       <c r="F21" s="3">
-        <v>1752200</v>
+        <v>1619100</v>
       </c>
       <c r="G21" s="3">
-        <v>1974100</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
+        <v>1783800</v>
+      </c>
+      <c r="H21" s="3">
+        <v>2008900</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>3</v>
@@ -1035,90 +1071,102 @@
       <c r="J21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K21" s="3"/>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L21" s="3"/>
+    </row>
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>15600</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E22" s="3">
-        <v>16500</v>
+        <v>15900</v>
       </c>
       <c r="F22" s="3">
-        <v>28000</v>
+        <v>16800</v>
       </c>
       <c r="G22" s="3">
-        <v>24300</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
+        <v>28500</v>
+      </c>
+      <c r="H22" s="3">
+        <v>24700</v>
+      </c>
+      <c r="I22" s="3">
+        <v>13000</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3"/>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L22" s="3"/>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>769200</v>
+        <v>430300</v>
       </c>
       <c r="E23" s="3">
-        <v>996000</v>
+        <v>780800</v>
       </c>
       <c r="F23" s="3">
-        <v>1155200</v>
+        <v>1011000</v>
       </c>
       <c r="G23" s="3">
-        <v>1398700</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>3</v>
+        <v>1172600</v>
+      </c>
+      <c r="H23" s="3">
+        <v>1419700</v>
+      </c>
+      <c r="I23" s="3">
+        <v>1396900</v>
       </c>
       <c r="J23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K23" s="3"/>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L23" s="3"/>
+    </row>
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>184800</v>
+        <v>119200</v>
       </c>
       <c r="E24" s="3">
-        <v>254900</v>
+        <v>187600</v>
       </c>
       <c r="F24" s="3">
-        <v>303800</v>
+        <v>258700</v>
       </c>
       <c r="G24" s="3">
-        <v>399800</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
+        <v>308400</v>
+      </c>
+      <c r="H24" s="3">
+        <v>405900</v>
+      </c>
+      <c r="I24" s="3">
+        <v>347300</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3"/>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L24" s="3"/>
+    </row>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1143,63 +1191,72 @@
       <c r="J25" s="3">
         <v>0</v>
       </c>
-      <c r="K25" s="3"/>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K25" s="3">
+        <v>0</v>
+      </c>
+      <c r="L25" s="3"/>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>584500</v>
+        <v>311100</v>
       </c>
       <c r="E26" s="3">
-        <v>741100</v>
+        <v>593300</v>
       </c>
       <c r="F26" s="3">
-        <v>851300</v>
+        <v>752300</v>
       </c>
       <c r="G26" s="3">
-        <v>998800</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>3</v>
+        <v>864100</v>
+      </c>
+      <c r="H26" s="3">
+        <v>1013900</v>
+      </c>
+      <c r="I26" s="3">
+        <v>1049500</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K26" s="3"/>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L26" s="3"/>
+    </row>
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>573100</v>
+        <v>295700</v>
       </c>
       <c r="E27" s="3">
-        <v>729300</v>
+        <v>581800</v>
       </c>
       <c r="F27" s="3">
-        <v>838500</v>
+        <v>740300</v>
       </c>
       <c r="G27" s="3">
-        <v>984700</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>3</v>
+        <v>851200</v>
+      </c>
+      <c r="H27" s="3">
+        <v>999500</v>
+      </c>
+      <c r="I27" s="3">
+        <v>1038500</v>
       </c>
       <c r="J27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K27" s="3"/>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L27" s="3"/>
+    </row>
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1224,36 +1281,42 @@
       <c r="J28" s="3">
         <v>0</v>
       </c>
-      <c r="K28" s="3"/>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K28" s="3">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3"/>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3">
+      <c r="D29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E29" s="3">
         <v>-1900</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>-1300</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-1000</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-500</v>
       </c>
-      <c r="H29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>3</v>
+      <c r="I29" s="3">
+        <v>-2600</v>
       </c>
       <c r="J29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K29" s="3"/>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L29" s="3"/>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1278,9 +1341,12 @@
       <c r="J30" s="3">
         <v>0</v>
       </c>
-      <c r="K30" s="3"/>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K30" s="3">
+        <v>0</v>
+      </c>
+      <c r="L30" s="3"/>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1305,63 +1371,72 @@
       <c r="J31" s="3">
         <v>0</v>
       </c>
-      <c r="K31" s="3"/>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K31" s="3">
+        <v>0</v>
+      </c>
+      <c r="L31" s="3"/>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-54000</v>
+        <v>-25700</v>
       </c>
       <c r="E32" s="3">
-        <v>-59600</v>
+        <v>-54800</v>
       </c>
       <c r="F32" s="3">
-        <v>-17500</v>
+        <v>-60500</v>
       </c>
       <c r="G32" s="3">
-        <v>-17200</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
+        <v>-17700</v>
+      </c>
+      <c r="H32" s="3">
+        <v>-17400</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-9900</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K32" s="3"/>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L32" s="3"/>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>571300</v>
+        <v>295700</v>
       </c>
       <c r="E33" s="3">
-        <v>728000</v>
+        <v>579900</v>
       </c>
       <c r="F33" s="3">
-        <v>837600</v>
+        <v>738900</v>
       </c>
       <c r="G33" s="3">
-        <v>984100</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>3</v>
+        <v>850200</v>
+      </c>
+      <c r="H33" s="3">
+        <v>999000</v>
+      </c>
+      <c r="I33" s="3">
+        <v>1035900</v>
       </c>
       <c r="J33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K33" s="3"/>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L33" s="3"/>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1386,68 +1461,77 @@
       <c r="J34" s="3">
         <v>0</v>
       </c>
-      <c r="K34" s="3"/>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K34" s="3">
+        <v>0</v>
+      </c>
+      <c r="L34" s="3"/>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>571300</v>
+        <v>295700</v>
       </c>
       <c r="E35" s="3">
-        <v>728000</v>
+        <v>579900</v>
       </c>
       <c r="F35" s="3">
-        <v>837600</v>
+        <v>738900</v>
       </c>
       <c r="G35" s="3">
-        <v>984100</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>3</v>
+        <v>850200</v>
+      </c>
+      <c r="H35" s="3">
+        <v>999000</v>
+      </c>
+      <c r="I35" s="3">
+        <v>1035900</v>
       </c>
       <c r="J35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K35" s="3"/>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L35" s="3"/>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>3</v>
+      <c r="I38" s="2">
+        <v>43465</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K38" s="2"/>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L38" s="2"/>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1459,8 +1543,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1472,25 +1557,26 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1668300</v>
+        <v>1965800</v>
       </c>
       <c r="E41" s="3">
-        <v>2085400</v>
+        <v>1693400</v>
       </c>
       <c r="F41" s="3">
-        <v>2180400</v>
+        <v>2116800</v>
       </c>
       <c r="G41" s="3">
-        <v>1592100</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>3</v>
+        <v>2213300</v>
+      </c>
+      <c r="H41" s="3">
+        <v>1616100</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>3</v>
@@ -1498,26 +1584,29 @@
       <c r="J41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K41" s="3"/>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L41" s="3"/>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>136800</v>
+        <v>44500</v>
       </c>
       <c r="E42" s="3">
-        <v>186500</v>
+        <v>138900</v>
       </c>
       <c r="F42" s="3">
-        <v>212900</v>
+        <v>189400</v>
       </c>
       <c r="G42" s="3">
-        <v>422900</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>3</v>
+        <v>216100</v>
+      </c>
+      <c r="H42" s="3">
+        <v>429300</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>3</v>
@@ -1525,26 +1614,29 @@
       <c r="J42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K42" s="3"/>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L42" s="3"/>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1558900</v>
+        <v>1557700</v>
       </c>
       <c r="E43" s="3">
-        <v>1452300</v>
+        <v>1582400</v>
       </c>
       <c r="F43" s="3">
-        <v>1342400</v>
+        <v>1474200</v>
       </c>
       <c r="G43" s="3">
-        <v>1402900</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
+        <v>1362600</v>
+      </c>
+      <c r="H43" s="3">
+        <v>1424000</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>3</v>
@@ -1552,26 +1644,29 @@
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K43" s="3"/>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L43" s="3"/>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1848500</v>
+        <v>1778100</v>
       </c>
       <c r="E44" s="3">
-        <v>1514400</v>
+        <v>1876300</v>
       </c>
       <c r="F44" s="3">
-        <v>1312300</v>
+        <v>1537200</v>
       </c>
       <c r="G44" s="3">
-        <v>1325800</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>3</v>
+        <v>1332100</v>
+      </c>
+      <c r="H44" s="3">
+        <v>1345800</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>3</v>
@@ -1579,26 +1674,29 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3"/>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L44" s="3"/>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>147400</v>
+        <v>161200</v>
       </c>
       <c r="E45" s="3">
-        <v>138400</v>
+        <v>149600</v>
       </c>
       <c r="F45" s="3">
-        <v>120500</v>
+        <v>140500</v>
       </c>
       <c r="G45" s="3">
-        <v>150100</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
+        <v>122300</v>
+      </c>
+      <c r="H45" s="3">
+        <v>152400</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
@@ -1606,26 +1704,29 @@
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3"/>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3"/>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>5359800</v>
+        <v>5507300</v>
       </c>
       <c r="E46" s="3">
-        <v>5377000</v>
+        <v>5440600</v>
       </c>
       <c r="F46" s="3">
-        <v>5168500</v>
+        <v>5458000</v>
       </c>
       <c r="G46" s="3">
-        <v>4893900</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>3</v>
+        <v>5246400</v>
+      </c>
+      <c r="H46" s="3">
+        <v>4967600</v>
       </c>
       <c r="I46" s="3" t="s">
         <v>3</v>
@@ -1633,26 +1734,29 @@
       <c r="J46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K46" s="3"/>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L46" s="3"/>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>241600</v>
+        <v>260800</v>
       </c>
       <c r="E47" s="3">
-        <v>223400</v>
+        <v>245200</v>
       </c>
       <c r="F47" s="3">
-        <v>214200</v>
+        <v>226700</v>
       </c>
       <c r="G47" s="3">
-        <v>228400</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
+        <v>217500</v>
+      </c>
+      <c r="H47" s="3">
+        <v>231800</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>3</v>
@@ -1660,26 +1764,29 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3"/>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3"/>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>3837600</v>
+        <v>3685500</v>
       </c>
       <c r="E48" s="3">
-        <v>3802500</v>
+        <v>3895400</v>
       </c>
       <c r="F48" s="3">
-        <v>3854200</v>
+        <v>3859800</v>
       </c>
       <c r="G48" s="3">
-        <v>3995000</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
+        <v>3912300</v>
+      </c>
+      <c r="H48" s="3">
+        <v>4055100</v>
       </c>
       <c r="I48" s="3" t="s">
         <v>3</v>
@@ -1687,26 +1794,29 @@
       <c r="J48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K48" s="3"/>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L48" s="3"/>
+    </row>
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1673600</v>
+        <v>2026300</v>
       </c>
       <c r="E49" s="3">
-        <v>1567900</v>
+        <v>1698800</v>
       </c>
       <c r="F49" s="3">
-        <v>1495900</v>
+        <v>1591500</v>
       </c>
       <c r="G49" s="3">
-        <v>1510400</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>3</v>
+        <v>1518400</v>
+      </c>
+      <c r="H49" s="3">
+        <v>1533200</v>
       </c>
       <c r="I49" s="3" t="s">
         <v>3</v>
@@ -1714,9 +1824,12 @@
       <c r="J49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K49" s="3"/>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L49" s="3"/>
+    </row>
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1741,9 +1854,12 @@
       <c r="J50" s="3">
         <v>0</v>
       </c>
-      <c r="K50" s="3"/>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K50" s="3">
+        <v>0</v>
+      </c>
+      <c r="L50" s="3"/>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1768,26 +1884,29 @@
       <c r="J51" s="3">
         <v>0</v>
       </c>
-      <c r="K51" s="3"/>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K51" s="3">
+        <v>0</v>
+      </c>
+      <c r="L51" s="3"/>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>350300</v>
+        <v>448100</v>
       </c>
       <c r="E52" s="3">
-        <v>343800</v>
+        <v>355600</v>
       </c>
       <c r="F52" s="3">
-        <v>326800</v>
+        <v>349000</v>
       </c>
       <c r="G52" s="3">
-        <v>354400</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
+        <v>331700</v>
+      </c>
+      <c r="H52" s="3">
+        <v>359700</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>3</v>
@@ -1795,9 +1914,12 @@
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K52" s="3"/>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L52" s="3"/>
+    </row>
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1822,26 +1944,29 @@
       <c r="J53" s="3">
         <v>0</v>
       </c>
-      <c r="K53" s="3"/>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K53" s="3">
+        <v>0</v>
+      </c>
+      <c r="L53" s="3"/>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>11463000</v>
+        <v>11928100</v>
       </c>
       <c r="E54" s="3">
-        <v>11314600</v>
+        <v>11635600</v>
       </c>
       <c r="F54" s="3">
-        <v>11059700</v>
+        <v>11485000</v>
       </c>
       <c r="G54" s="3">
-        <v>10982000</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>3</v>
+        <v>11226300</v>
+      </c>
+      <c r="H54" s="3">
+        <v>11147400</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>3</v>
@@ -1849,9 +1974,12 @@
       <c r="J54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K54" s="3"/>
-    </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L54" s="3"/>
+    </row>
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1863,8 +1991,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1876,25 +2005,26 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1143200</v>
+        <v>1587400</v>
       </c>
       <c r="E57" s="3">
-        <v>1035700</v>
+        <v>1160400</v>
       </c>
       <c r="F57" s="3">
-        <v>914200</v>
+        <v>1051300</v>
       </c>
       <c r="G57" s="3">
-        <v>961900</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
+        <v>928000</v>
+      </c>
+      <c r="H57" s="3">
+        <v>976400</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>3</v>
@@ -1902,26 +2032,29 @@
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K57" s="3"/>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L57" s="3"/>
+    </row>
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>565100</v>
+        <v>222800</v>
       </c>
       <c r="E58" s="3">
-        <v>173200</v>
+        <v>573600</v>
       </c>
       <c r="F58" s="3">
-        <v>333700</v>
+        <v>175800</v>
       </c>
       <c r="G58" s="3">
-        <v>299800</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
+        <v>338700</v>
+      </c>
+      <c r="H58" s="3">
+        <v>304400</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>3</v>
@@ -1929,26 +2062,29 @@
       <c r="J58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K58" s="3"/>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L58" s="3"/>
+    </row>
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1522800</v>
+        <v>1289800</v>
       </c>
       <c r="E59" s="3">
-        <v>1592500</v>
+        <v>1545800</v>
       </c>
       <c r="F59" s="3">
-        <v>1576800</v>
+        <v>1616500</v>
       </c>
       <c r="G59" s="3">
-        <v>1610200</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
+        <v>1600600</v>
+      </c>
+      <c r="H59" s="3">
+        <v>1634500</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>3</v>
@@ -1956,26 +2092,29 @@
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K59" s="3"/>
-    </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L59" s="3"/>
+    </row>
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>3231200</v>
+        <v>3100000</v>
       </c>
       <c r="E60" s="3">
-        <v>2801400</v>
+        <v>3279800</v>
       </c>
       <c r="F60" s="3">
-        <v>2824700</v>
+        <v>2843600</v>
       </c>
       <c r="G60" s="3">
-        <v>2872000</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>3</v>
+        <v>2867200</v>
+      </c>
+      <c r="H60" s="3">
+        <v>2915200</v>
       </c>
       <c r="I60" s="3" t="s">
         <v>3</v>
@@ -1983,26 +2122,29 @@
       <c r="J60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K60" s="3"/>
-    </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L60" s="3"/>
+    </row>
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1180500</v>
+        <v>1536800</v>
       </c>
       <c r="E61" s="3">
-        <v>1610800</v>
+        <v>1198200</v>
       </c>
       <c r="F61" s="3">
-        <v>1487100</v>
+        <v>1635100</v>
       </c>
       <c r="G61" s="3">
-        <v>1614000</v>
+        <v>1509400</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>1638300</v>
       </c>
       <c r="I61" s="3">
         <v>0</v>
@@ -2010,26 +2152,29 @@
       <c r="J61" s="3">
         <v>0</v>
       </c>
-      <c r="K61" s="3"/>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3"/>
+    </row>
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>442000</v>
+        <v>470200</v>
       </c>
       <c r="E62" s="3">
-        <v>369400</v>
+        <v>448600</v>
       </c>
       <c r="F62" s="3">
-        <v>518300</v>
+        <v>375000</v>
       </c>
       <c r="G62" s="3">
-        <v>709800</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
+        <v>526200</v>
+      </c>
+      <c r="H62" s="3">
+        <v>720500</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
@@ -2037,9 +2182,12 @@
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K62" s="3"/>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L62" s="3"/>
+    </row>
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2064,9 +2212,12 @@
       <c r="J63" s="3">
         <v>0</v>
       </c>
-      <c r="K63" s="3"/>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K63" s="3">
+        <v>0</v>
+      </c>
+      <c r="L63" s="3"/>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2091,9 +2242,12 @@
       <c r="J64" s="3">
         <v>0</v>
       </c>
-      <c r="K64" s="3"/>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K64" s="3">
+        <v>0</v>
+      </c>
+      <c r="L64" s="3"/>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2118,26 +2272,29 @@
       <c r="J65" s="3">
         <v>0</v>
       </c>
-      <c r="K65" s="3"/>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K65" s="3">
+        <v>0</v>
+      </c>
+      <c r="L65" s="3"/>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>5008500</v>
+        <v>5298200</v>
       </c>
       <c r="E66" s="3">
-        <v>4906100</v>
+        <v>5083900</v>
       </c>
       <c r="F66" s="3">
-        <v>4926400</v>
+        <v>4980000</v>
       </c>
       <c r="G66" s="3">
-        <v>5286900</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>3</v>
+        <v>5000600</v>
+      </c>
+      <c r="H66" s="3">
+        <v>5366500</v>
       </c>
       <c r="I66" s="3" t="s">
         <v>3</v>
@@ -2145,9 +2302,12 @@
       <c r="J66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K66" s="3"/>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L66" s="3"/>
+    </row>
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2159,8 +2319,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2185,9 +2346,12 @@
       <c r="J68" s="3">
         <v>0</v>
       </c>
-      <c r="K68" s="3"/>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K68" s="3">
+        <v>0</v>
+      </c>
+      <c r="L68" s="3"/>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2212,9 +2376,12 @@
       <c r="J69" s="3">
         <v>0</v>
       </c>
-      <c r="K69" s="3"/>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K69" s="3">
+        <v>0</v>
+      </c>
+      <c r="L69" s="3"/>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2239,9 +2406,12 @@
       <c r="J70" s="3">
         <v>0</v>
       </c>
-      <c r="K70" s="3"/>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3"/>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2266,26 +2436,29 @@
       <c r="J71" s="3">
         <v>0</v>
       </c>
-      <c r="K71" s="3"/>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K71" s="3">
+        <v>0</v>
+      </c>
+      <c r="L71" s="3"/>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>4916500</v>
+        <v>4797500</v>
       </c>
       <c r="E72" s="3">
-        <v>5192100</v>
+        <v>4990500</v>
       </c>
       <c r="F72" s="3">
-        <v>5173600</v>
+        <v>5270300</v>
       </c>
       <c r="G72" s="3">
-        <v>4656500</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
+        <v>5251500</v>
+      </c>
+      <c r="H72" s="3">
+        <v>4726700</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>3</v>
@@ -2293,9 +2466,12 @@
       <c r="J72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K72" s="3"/>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L72" s="3"/>
+    </row>
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2320,9 +2496,12 @@
       <c r="J73" s="3">
         <v>0</v>
       </c>
-      <c r="K73" s="3"/>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K73" s="3">
+        <v>0</v>
+      </c>
+      <c r="L73" s="3"/>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2347,9 +2526,12 @@
       <c r="J74" s="3">
         <v>0</v>
       </c>
-      <c r="K74" s="3"/>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K74" s="3">
+        <v>0</v>
+      </c>
+      <c r="L74" s="3"/>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2374,26 +2556,29 @@
       <c r="J75" s="3">
         <v>0</v>
       </c>
-      <c r="K75" s="3"/>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K75" s="3">
+        <v>0</v>
+      </c>
+      <c r="L75" s="3"/>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>6454500</v>
+        <v>6629900</v>
       </c>
       <c r="E76" s="3">
-        <v>6408500</v>
+        <v>6551700</v>
       </c>
       <c r="F76" s="3">
-        <v>6133300</v>
+        <v>6505000</v>
       </c>
       <c r="G76" s="3">
-        <v>5695100</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>3</v>
+        <v>6225700</v>
+      </c>
+      <c r="H76" s="3">
+        <v>5780900</v>
       </c>
       <c r="I76" s="3" t="s">
         <v>3</v>
@@ -2401,9 +2586,12 @@
       <c r="J76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K76" s="3"/>
-    </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L76" s="3"/>
+    </row>
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2428,68 +2616,77 @@
       <c r="J77" s="3">
         <v>0</v>
       </c>
-      <c r="K77" s="3"/>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K77" s="3">
+        <v>0</v>
+      </c>
+      <c r="L77" s="3"/>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I80" s="2" t="s">
-        <v>3</v>
+      <c r="I80" s="2">
+        <v>43465</v>
       </c>
       <c r="J80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K80" s="2"/>
-    </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L80" s="2"/>
+    </row>
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>571300</v>
+        <v>295700</v>
       </c>
       <c r="E81" s="3">
-        <v>728000</v>
+        <v>579900</v>
       </c>
       <c r="F81" s="3">
-        <v>837600</v>
+        <v>738900</v>
       </c>
       <c r="G81" s="3">
-        <v>984100</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>3</v>
+        <v>850200</v>
+      </c>
+      <c r="H81" s="3">
+        <v>999000</v>
+      </c>
+      <c r="I81" s="3">
+        <v>1035900</v>
       </c>
       <c r="J81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K81" s="3"/>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L81" s="3"/>
+    </row>
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2501,25 +2698,26 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>595900</v>
+        <v>603900</v>
       </c>
       <c r="E83" s="3">
-        <v>579900</v>
+        <v>604800</v>
       </c>
       <c r="F83" s="3">
-        <v>571600</v>
+        <v>588700</v>
       </c>
       <c r="G83" s="3">
-        <v>553600</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
+        <v>580200</v>
+      </c>
+      <c r="H83" s="3">
+        <v>561900</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>3</v>
@@ -2527,9 +2725,12 @@
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K83" s="3"/>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L83" s="3"/>
+    </row>
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2554,9 +2755,12 @@
       <c r="J84" s="3">
         <v>0</v>
       </c>
-      <c r="K84" s="3"/>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K84" s="3">
+        <v>0</v>
+      </c>
+      <c r="L84" s="3"/>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2581,9 +2785,12 @@
       <c r="J85" s="3">
         <v>0</v>
       </c>
-      <c r="K85" s="3"/>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K85" s="3">
+        <v>0</v>
+      </c>
+      <c r="L85" s="3"/>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2608,9 +2815,12 @@
       <c r="J86" s="3">
         <v>0</v>
       </c>
-      <c r="K86" s="3"/>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K86" s="3">
+        <v>0</v>
+      </c>
+      <c r="L86" s="3"/>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2635,9 +2845,12 @@
       <c r="J87" s="3">
         <v>0</v>
       </c>
-      <c r="K87" s="3"/>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K87" s="3">
+        <v>0</v>
+      </c>
+      <c r="L87" s="3"/>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2662,26 +2875,29 @@
       <c r="J88" s="3">
         <v>0</v>
       </c>
-      <c r="K88" s="3"/>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K88" s="3">
+        <v>0</v>
+      </c>
+      <c r="L88" s="3"/>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>869200</v>
+        <v>1364700</v>
       </c>
       <c r="E89" s="3">
-        <v>1165500</v>
+        <v>882300</v>
       </c>
       <c r="F89" s="3">
-        <v>1425700</v>
+        <v>1183000</v>
       </c>
       <c r="G89" s="3">
-        <v>1623600</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
+        <v>1447200</v>
+      </c>
+      <c r="H89" s="3">
+        <v>1648100</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>3</v>
@@ -2689,9 +2905,12 @@
       <c r="J89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K89" s="3"/>
-    </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L89" s="3"/>
+    </row>
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2703,25 +2922,26 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-435100</v>
+        <v>-365100</v>
       </c>
       <c r="E91" s="3">
-        <v>-398100</v>
+        <v>-441600</v>
       </c>
       <c r="F91" s="3">
-        <v>-394400</v>
+        <v>-404100</v>
       </c>
       <c r="G91" s="3">
-        <v>-557500</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>3</v>
+        <v>-400300</v>
+      </c>
+      <c r="H91" s="3">
+        <v>-565900</v>
       </c>
       <c r="I91" s="3" t="s">
         <v>3</v>
@@ -2729,9 +2949,12 @@
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K91" s="3"/>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L91" s="3"/>
+    </row>
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2756,9 +2979,12 @@
       <c r="J92" s="3">
         <v>0</v>
       </c>
-      <c r="K92" s="3"/>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K92" s="3">
+        <v>0</v>
+      </c>
+      <c r="L92" s="3"/>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2783,26 +3009,29 @@
       <c r="J93" s="3">
         <v>0</v>
       </c>
-      <c r="K93" s="3"/>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K93" s="3">
+        <v>0</v>
+      </c>
+      <c r="L93" s="3"/>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-497400</v>
+        <v>-736700</v>
       </c>
       <c r="E94" s="3">
-        <v>-446400</v>
+        <v>-504900</v>
       </c>
       <c r="F94" s="3">
-        <v>-411300</v>
+        <v>-453100</v>
       </c>
       <c r="G94" s="3">
-        <v>-625900</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
+        <v>-417500</v>
+      </c>
+      <c r="H94" s="3">
+        <v>-635400</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>3</v>
@@ -2810,9 +3039,12 @@
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K94" s="3"/>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L94" s="3"/>
+    </row>
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2824,25 +3056,26 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-457700</v>
+        <v>-467300</v>
       </c>
       <c r="E96" s="3">
-        <v>-450600</v>
+        <v>-464600</v>
       </c>
       <c r="F96" s="3">
-        <v>-431500</v>
+        <v>-457400</v>
       </c>
       <c r="G96" s="3">
-        <v>-401800</v>
+        <v>-438000</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>-407900</v>
       </c>
       <c r="I96" s="3">
         <v>0</v>
@@ -2850,9 +3083,12 @@
       <c r="J96" s="3">
         <v>0</v>
       </c>
-      <c r="K96" s="3"/>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3"/>
+    </row>
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -2877,9 +3113,12 @@
       <c r="J97" s="3">
         <v>0</v>
       </c>
-      <c r="K97" s="3"/>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K97" s="3">
+        <v>0</v>
+      </c>
+      <c r="L97" s="3"/>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -2904,9 +3143,12 @@
       <c r="J98" s="3">
         <v>0</v>
       </c>
-      <c r="K98" s="3"/>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K98" s="3">
+        <v>0</v>
+      </c>
+      <c r="L98" s="3"/>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -2931,26 +3173,29 @@
       <c r="J99" s="3">
         <v>0</v>
       </c>
-      <c r="K99" s="3"/>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K99" s="3">
+        <v>0</v>
+      </c>
+      <c r="L99" s="3"/>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-925000</v>
+        <v>-539100</v>
       </c>
       <c r="E100" s="3">
-        <v>-940000</v>
+        <v>-939000</v>
       </c>
       <c r="F100" s="3">
-        <v>-578100</v>
+        <v>-954200</v>
       </c>
       <c r="G100" s="3">
-        <v>-837700</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
+        <v>-586800</v>
+      </c>
+      <c r="H100" s="3">
+        <v>-850400</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>3</v>
@@ -2958,53 +3203,59 @@
       <c r="J100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K100" s="3"/>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L100" s="3"/>
+    </row>
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>102900</v>
+        <v>68900</v>
       </c>
       <c r="E101" s="3">
-        <v>107400</v>
+        <v>104400</v>
       </c>
       <c r="F101" s="3">
-        <v>-14700</v>
+        <v>109000</v>
       </c>
       <c r="G101" s="3">
+        <v>-14900</v>
+      </c>
+      <c r="H101" s="3">
         <v>-2600</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3"/>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3"/>
+    </row>
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-450300</v>
+        <v>157800</v>
       </c>
       <c r="E102" s="3">
-        <v>-113600</v>
+        <v>-457100</v>
       </c>
       <c r="F102" s="3">
-        <v>421600</v>
+        <v>-115300</v>
       </c>
       <c r="G102" s="3">
-        <v>157400</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>3</v>
+        <v>428000</v>
+      </c>
+      <c r="H102" s="3">
+        <v>159800</v>
       </c>
       <c r="I102" s="3" t="s">
         <v>3</v>
@@ -3012,7 +3263,10 @@
       <c r="J102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K102" s="3"/>
+      <c r="K102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/KAOOY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/KAOOY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="92">
   <si>
     <t>KAOOY</t>
   </si>
@@ -712,22 +712,22 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>10329600</v>
+        <v>9777900</v>
       </c>
       <c r="E8" s="3">
-        <v>10454100</v>
+        <v>9895800</v>
       </c>
       <c r="F8" s="3">
-        <v>9562500</v>
+        <v>9051700</v>
       </c>
       <c r="G8" s="3">
-        <v>9314700</v>
+        <v>8817100</v>
       </c>
       <c r="H8" s="3">
-        <v>10125100</v>
+        <v>9584300</v>
       </c>
       <c r="I8" s="3">
-        <v>10164000</v>
+        <v>9621100</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>3</v>
@@ -742,22 +742,22 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>6552300</v>
+        <v>6202300</v>
       </c>
       <c r="E9" s="3">
-        <v>6758300</v>
+        <v>6397300</v>
       </c>
       <c r="F9" s="3">
-        <v>5699200</v>
+        <v>5394800</v>
       </c>
       <c r="G9" s="3">
-        <v>5333400</v>
+        <v>5048500</v>
       </c>
       <c r="H9" s="3">
-        <v>5720400</v>
+        <v>5414900</v>
       </c>
       <c r="I9" s="3">
-        <v>5755900</v>
+        <v>5448400</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>3</v>
@@ -772,22 +772,22 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>3777300</v>
+        <v>3575500</v>
       </c>
       <c r="E10" s="3">
-        <v>3695800</v>
+        <v>3498400</v>
       </c>
       <c r="F10" s="3">
-        <v>3863300</v>
+        <v>3657000</v>
       </c>
       <c r="G10" s="3">
-        <v>3981300</v>
+        <v>3768600</v>
       </c>
       <c r="H10" s="3">
-        <v>4404700</v>
+        <v>4169400</v>
       </c>
       <c r="I10" s="3">
-        <v>4408100</v>
+        <v>4172600</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>3</v>
@@ -816,22 +816,22 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>421800</v>
+        <v>399200</v>
       </c>
       <c r="E12" s="3">
-        <v>408500</v>
+        <v>386600</v>
       </c>
       <c r="F12" s="3">
-        <v>397600</v>
+        <v>376400</v>
       </c>
       <c r="G12" s="3">
-        <v>394400</v>
+        <v>373300</v>
       </c>
       <c r="H12" s="3">
-        <v>398600</v>
+        <v>377300</v>
       </c>
       <c r="I12" s="3">
-        <v>388700</v>
+        <v>368000</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>3</v>
@@ -875,23 +875,23 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>138500</v>
       </c>
       <c r="E14" s="3">
         <v>200</v>
       </c>
       <c r="F14" s="3">
-        <v>30700</v>
+        <v>29000</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H14" s="3">
-        <v>5100</v>
+        <v>4800</v>
       </c>
       <c r="I14" s="3">
-        <v>10200</v>
+        <v>9700</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
@@ -906,22 +906,22 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>187500</v>
+        <v>177500</v>
       </c>
       <c r="E15" s="3">
-        <v>178600</v>
+        <v>169100</v>
       </c>
       <c r="F15" s="3">
-        <v>176500</v>
+        <v>167100</v>
       </c>
       <c r="G15" s="3">
-        <v>183400</v>
+        <v>173700</v>
       </c>
       <c r="H15" s="3">
-        <v>180100</v>
+        <v>170500</v>
       </c>
       <c r="I15" s="3">
-        <v>108200</v>
+        <v>102400</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>3</v>
@@ -947,22 +947,22 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>9924900</v>
+        <v>9394800</v>
       </c>
       <c r="E17" s="3">
-        <v>9712300</v>
+        <v>9193500</v>
       </c>
       <c r="F17" s="3">
-        <v>8595200</v>
+        <v>8136100</v>
       </c>
       <c r="G17" s="3">
-        <v>8131400</v>
+        <v>7697000</v>
       </c>
       <c r="H17" s="3">
-        <v>8698100</v>
+        <v>8233500</v>
       </c>
       <c r="I17" s="3">
-        <v>8764000</v>
+        <v>8295900</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>3</v>
@@ -977,22 +977,22 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>404600</v>
+        <v>383000</v>
       </c>
       <c r="E18" s="3">
-        <v>741900</v>
+        <v>702300</v>
       </c>
       <c r="F18" s="3">
-        <v>967300</v>
+        <v>915600</v>
       </c>
       <c r="G18" s="3">
-        <v>1183300</v>
+        <v>1120100</v>
       </c>
       <c r="H18" s="3">
-        <v>1427000</v>
+        <v>1350800</v>
       </c>
       <c r="I18" s="3">
-        <v>1399900</v>
+        <v>1325100</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>3</v>
@@ -1021,22 +1021,22 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>25700</v>
+        <v>45900</v>
       </c>
       <c r="E20" s="3">
-        <v>54800</v>
+        <v>51900</v>
       </c>
       <c r="F20" s="3">
-        <v>60500</v>
+        <v>57300</v>
       </c>
       <c r="G20" s="3">
-        <v>17700</v>
+        <v>16800</v>
       </c>
       <c r="H20" s="3">
-        <v>17400</v>
+        <v>16500</v>
       </c>
       <c r="I20" s="3">
-        <v>9900</v>
+        <v>9400</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>3</v>
@@ -1051,19 +1051,19 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1036900</v>
+        <v>999600</v>
       </c>
       <c r="E21" s="3">
-        <v>1404200</v>
+        <v>1325800</v>
       </c>
       <c r="F21" s="3">
-        <v>1619100</v>
+        <v>1529200</v>
       </c>
       <c r="G21" s="3">
-        <v>1783800</v>
+        <v>1685200</v>
       </c>
       <c r="H21" s="3">
-        <v>2008900</v>
+        <v>1898400</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>3</v>
@@ -1080,23 +1080,23 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>3</v>
+      <c r="D22" s="3">
+        <v>21600</v>
       </c>
       <c r="E22" s="3">
+        <v>15000</v>
+      </c>
+      <c r="F22" s="3">
         <v>15900</v>
       </c>
-      <c r="F22" s="3">
-        <v>16800</v>
-      </c>
       <c r="G22" s="3">
-        <v>28500</v>
+        <v>26900</v>
       </c>
       <c r="H22" s="3">
-        <v>24700</v>
+        <v>23400</v>
       </c>
       <c r="I22" s="3">
-        <v>13000</v>
+        <v>12300</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>3</v>
@@ -1111,22 +1111,22 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>430300</v>
+        <v>407300</v>
       </c>
       <c r="E23" s="3">
-        <v>780800</v>
+        <v>739100</v>
       </c>
       <c r="F23" s="3">
-        <v>1011000</v>
+        <v>957000</v>
       </c>
       <c r="G23" s="3">
-        <v>1172600</v>
+        <v>1109900</v>
       </c>
       <c r="H23" s="3">
-        <v>1419700</v>
+        <v>1343900</v>
       </c>
       <c r="I23" s="3">
-        <v>1396900</v>
+        <v>1322300</v>
       </c>
       <c r="J23" s="3" t="s">
         <v>3</v>
@@ -1141,22 +1141,22 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>119200</v>
+        <v>111400</v>
       </c>
       <c r="E24" s="3">
-        <v>187600</v>
+        <v>177500</v>
       </c>
       <c r="F24" s="3">
-        <v>258700</v>
+        <v>244900</v>
       </c>
       <c r="G24" s="3">
-        <v>308400</v>
+        <v>291900</v>
       </c>
       <c r="H24" s="3">
-        <v>405900</v>
+        <v>384200</v>
       </c>
       <c r="I24" s="3">
-        <v>347300</v>
+        <v>328800</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
@@ -1201,22 +1201,22 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>311100</v>
+        <v>295900</v>
       </c>
       <c r="E26" s="3">
-        <v>593300</v>
+        <v>561600</v>
       </c>
       <c r="F26" s="3">
-        <v>752300</v>
+        <v>712100</v>
       </c>
       <c r="G26" s="3">
-        <v>864100</v>
+        <v>818000</v>
       </c>
       <c r="H26" s="3">
-        <v>1013900</v>
+        <v>959700</v>
       </c>
       <c r="I26" s="3">
-        <v>1049500</v>
+        <v>993500</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>3</v>
@@ -1231,22 +1231,22 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>295700</v>
+        <v>281400</v>
       </c>
       <c r="E27" s="3">
-        <v>581800</v>
+        <v>550700</v>
       </c>
       <c r="F27" s="3">
-        <v>740300</v>
+        <v>700700</v>
       </c>
       <c r="G27" s="3">
-        <v>851200</v>
+        <v>805700</v>
       </c>
       <c r="H27" s="3">
-        <v>999500</v>
+        <v>946100</v>
       </c>
       <c r="I27" s="3">
-        <v>1038500</v>
+        <v>983000</v>
       </c>
       <c r="J27" s="3" t="s">
         <v>3</v>
@@ -1290,23 +1290,23 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>3</v>
+      <c r="D29" s="3">
+        <v>-1500</v>
       </c>
       <c r="E29" s="3">
-        <v>-1900</v>
+        <v>-1800</v>
       </c>
       <c r="F29" s="3">
         <v>-1300</v>
       </c>
       <c r="G29" s="3">
-        <v>-1000</v>
+        <v>-900</v>
       </c>
       <c r="H29" s="3">
         <v>-500</v>
       </c>
       <c r="I29" s="3">
-        <v>-2600</v>
+        <v>-2500</v>
       </c>
       <c r="J29" s="3" t="s">
         <v>3</v>
@@ -1381,22 +1381,22 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-25700</v>
+        <v>-45900</v>
       </c>
       <c r="E32" s="3">
-        <v>-54800</v>
+        <v>-51900</v>
       </c>
       <c r="F32" s="3">
-        <v>-60500</v>
+        <v>-57300</v>
       </c>
       <c r="G32" s="3">
-        <v>-17700</v>
+        <v>-16800</v>
       </c>
       <c r="H32" s="3">
-        <v>-17400</v>
+        <v>-16500</v>
       </c>
       <c r="I32" s="3">
-        <v>-9900</v>
+        <v>-9400</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>3</v>
@@ -1411,22 +1411,22 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>295700</v>
+        <v>279900</v>
       </c>
       <c r="E33" s="3">
-        <v>579900</v>
+        <v>548900</v>
       </c>
       <c r="F33" s="3">
-        <v>738900</v>
+        <v>699500</v>
       </c>
       <c r="G33" s="3">
-        <v>850200</v>
+        <v>804800</v>
       </c>
       <c r="H33" s="3">
-        <v>999000</v>
+        <v>945600</v>
       </c>
       <c r="I33" s="3">
-        <v>1035900</v>
+        <v>980600</v>
       </c>
       <c r="J33" s="3" t="s">
         <v>3</v>
@@ -1471,22 +1471,22 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>295700</v>
+        <v>279900</v>
       </c>
       <c r="E35" s="3">
-        <v>579900</v>
+        <v>548900</v>
       </c>
       <c r="F35" s="3">
-        <v>738900</v>
+        <v>699500</v>
       </c>
       <c r="G35" s="3">
-        <v>850200</v>
+        <v>804800</v>
       </c>
       <c r="H35" s="3">
-        <v>999000</v>
+        <v>945600</v>
       </c>
       <c r="I35" s="3">
-        <v>1035900</v>
+        <v>980600</v>
       </c>
       <c r="J35" s="3" t="s">
         <v>3</v>
@@ -1564,19 +1564,19 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1965800</v>
+        <v>1828900</v>
       </c>
       <c r="E41" s="3">
-        <v>1693400</v>
+        <v>1603000</v>
       </c>
       <c r="F41" s="3">
-        <v>2116800</v>
+        <v>2003800</v>
       </c>
       <c r="G41" s="3">
-        <v>2213300</v>
+        <v>2095000</v>
       </c>
       <c r="H41" s="3">
-        <v>1616100</v>
+        <v>1529800</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>3</v>
@@ -1594,19 +1594,19 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>44500</v>
+        <v>74000</v>
       </c>
       <c r="E42" s="3">
-        <v>138900</v>
+        <v>131500</v>
       </c>
       <c r="F42" s="3">
-        <v>189400</v>
+        <v>179200</v>
       </c>
       <c r="G42" s="3">
-        <v>216100</v>
+        <v>204500</v>
       </c>
       <c r="H42" s="3">
-        <v>429300</v>
+        <v>406300</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>3</v>
@@ -1624,19 +1624,19 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1557700</v>
+        <v>1474500</v>
       </c>
       <c r="E43" s="3">
-        <v>1582400</v>
+        <v>1497900</v>
       </c>
       <c r="F43" s="3">
-        <v>1474200</v>
+        <v>1395400</v>
       </c>
       <c r="G43" s="3">
-        <v>1362600</v>
+        <v>1289900</v>
       </c>
       <c r="H43" s="3">
-        <v>1424000</v>
+        <v>1348000</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>3</v>
@@ -1654,19 +1654,19 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1778100</v>
+        <v>1683100</v>
       </c>
       <c r="E44" s="3">
-        <v>1876300</v>
+        <v>1776100</v>
       </c>
       <c r="F44" s="3">
-        <v>1537200</v>
+        <v>1455100</v>
       </c>
       <c r="G44" s="3">
-        <v>1332100</v>
+        <v>1260900</v>
       </c>
       <c r="H44" s="3">
-        <v>1345800</v>
+        <v>1273900</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>3</v>
@@ -1684,19 +1684,19 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>161200</v>
+        <v>152600</v>
       </c>
       <c r="E45" s="3">
-        <v>149600</v>
+        <v>141600</v>
       </c>
       <c r="F45" s="3">
-        <v>140500</v>
+        <v>133000</v>
       </c>
       <c r="G45" s="3">
-        <v>122300</v>
+        <v>115800</v>
       </c>
       <c r="H45" s="3">
-        <v>152400</v>
+        <v>144200</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
@@ -1714,19 +1714,19 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>5507300</v>
+        <v>5213200</v>
       </c>
       <c r="E46" s="3">
-        <v>5440600</v>
+        <v>5150000</v>
       </c>
       <c r="F46" s="3">
-        <v>5458000</v>
+        <v>5166500</v>
       </c>
       <c r="G46" s="3">
-        <v>5246400</v>
+        <v>4966200</v>
       </c>
       <c r="H46" s="3">
-        <v>4967600</v>
+        <v>4702200</v>
       </c>
       <c r="I46" s="3" t="s">
         <v>3</v>
@@ -1744,19 +1744,19 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>260800</v>
+        <v>246800</v>
       </c>
       <c r="E47" s="3">
-        <v>245200</v>
+        <v>232100</v>
       </c>
       <c r="F47" s="3">
-        <v>226700</v>
+        <v>214600</v>
       </c>
       <c r="G47" s="3">
-        <v>217500</v>
+        <v>205900</v>
       </c>
       <c r="H47" s="3">
-        <v>231800</v>
+        <v>219400</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>3</v>
@@ -1774,19 +1774,19 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>3685500</v>
+        <v>3488700</v>
       </c>
       <c r="E48" s="3">
-        <v>3895400</v>
+        <v>3687300</v>
       </c>
       <c r="F48" s="3">
-        <v>3859800</v>
+        <v>3653600</v>
       </c>
       <c r="G48" s="3">
-        <v>3912300</v>
+        <v>3703300</v>
       </c>
       <c r="H48" s="3">
-        <v>4055100</v>
+        <v>3838500</v>
       </c>
       <c r="I48" s="3" t="s">
         <v>3</v>
@@ -1804,19 +1804,19 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2026300</v>
+        <v>1918100</v>
       </c>
       <c r="E49" s="3">
-        <v>1698800</v>
+        <v>1608000</v>
       </c>
       <c r="F49" s="3">
-        <v>1591500</v>
+        <v>1506500</v>
       </c>
       <c r="G49" s="3">
-        <v>1518400</v>
+        <v>1437300</v>
       </c>
       <c r="H49" s="3">
-        <v>1533200</v>
+        <v>1451300</v>
       </c>
       <c r="I49" s="3" t="s">
         <v>3</v>
@@ -1894,19 +1894,19 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>448100</v>
+        <v>424200</v>
       </c>
       <c r="E52" s="3">
-        <v>355600</v>
+        <v>336600</v>
       </c>
       <c r="F52" s="3">
-        <v>349000</v>
+        <v>330300</v>
       </c>
       <c r="G52" s="3">
-        <v>331700</v>
+        <v>314000</v>
       </c>
       <c r="H52" s="3">
-        <v>359700</v>
+        <v>340500</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>3</v>
@@ -1954,19 +1954,19 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>11928100</v>
+        <v>11291000</v>
       </c>
       <c r="E54" s="3">
-        <v>11635600</v>
+        <v>11014100</v>
       </c>
       <c r="F54" s="3">
-        <v>11485000</v>
+        <v>10871600</v>
       </c>
       <c r="G54" s="3">
-        <v>11226300</v>
+        <v>10626600</v>
       </c>
       <c r="H54" s="3">
-        <v>11147400</v>
+        <v>10552000</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>3</v>
@@ -2012,19 +2012,19 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1587400</v>
+        <v>1033200</v>
       </c>
       <c r="E57" s="3">
-        <v>1160400</v>
+        <v>1098500</v>
       </c>
       <c r="F57" s="3">
-        <v>1051300</v>
+        <v>995200</v>
       </c>
       <c r="G57" s="3">
-        <v>928000</v>
+        <v>878400</v>
       </c>
       <c r="H57" s="3">
-        <v>976400</v>
+        <v>924200</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>3</v>
@@ -2042,19 +2042,19 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>222800</v>
+        <v>210900</v>
       </c>
       <c r="E58" s="3">
-        <v>573600</v>
+        <v>543000</v>
       </c>
       <c r="F58" s="3">
-        <v>175800</v>
+        <v>166400</v>
       </c>
       <c r="G58" s="3">
-        <v>338700</v>
+        <v>320600</v>
       </c>
       <c r="H58" s="3">
-        <v>304400</v>
+        <v>288100</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>3</v>
@@ -2072,19 +2072,19 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1289800</v>
+        <v>1690300</v>
       </c>
       <c r="E59" s="3">
-        <v>1545800</v>
+        <v>1463200</v>
       </c>
       <c r="F59" s="3">
-        <v>1616500</v>
+        <v>1530100</v>
       </c>
       <c r="G59" s="3">
-        <v>1600600</v>
+        <v>1515100</v>
       </c>
       <c r="H59" s="3">
-        <v>1634500</v>
+        <v>1547200</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>3</v>
@@ -2102,19 +2102,19 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>3100000</v>
+        <v>2934400</v>
       </c>
       <c r="E60" s="3">
-        <v>3279800</v>
+        <v>3104700</v>
       </c>
       <c r="F60" s="3">
-        <v>2843600</v>
+        <v>2691700</v>
       </c>
       <c r="G60" s="3">
-        <v>2867200</v>
+        <v>2714100</v>
       </c>
       <c r="H60" s="3">
-        <v>2915200</v>
+        <v>2759500</v>
       </c>
       <c r="I60" s="3" t="s">
         <v>3</v>
@@ -2132,19 +2132,19 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1536800</v>
+        <v>1454700</v>
       </c>
       <c r="E61" s="3">
-        <v>1198200</v>
+        <v>1134200</v>
       </c>
       <c r="F61" s="3">
-        <v>1635100</v>
+        <v>1547800</v>
       </c>
       <c r="G61" s="3">
-        <v>1509400</v>
+        <v>1428800</v>
       </c>
       <c r="H61" s="3">
-        <v>1638300</v>
+        <v>1550800</v>
       </c>
       <c r="I61" s="3">
         <v>0</v>
@@ -2162,19 +2162,19 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>470200</v>
+        <v>445000</v>
       </c>
       <c r="E62" s="3">
-        <v>448600</v>
+        <v>424700</v>
       </c>
       <c r="F62" s="3">
-        <v>375000</v>
+        <v>355000</v>
       </c>
       <c r="G62" s="3">
-        <v>526200</v>
+        <v>498000</v>
       </c>
       <c r="H62" s="3">
-        <v>720500</v>
+        <v>682000</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
@@ -2282,19 +2282,19 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>5298200</v>
+        <v>5015200</v>
       </c>
       <c r="E66" s="3">
-        <v>5083900</v>
+        <v>4812400</v>
       </c>
       <c r="F66" s="3">
-        <v>4980000</v>
+        <v>4714000</v>
       </c>
       <c r="G66" s="3">
-        <v>5000600</v>
+        <v>4733500</v>
       </c>
       <c r="H66" s="3">
-        <v>5366500</v>
+        <v>5079900</v>
       </c>
       <c r="I66" s="3" t="s">
         <v>3</v>
@@ -2446,19 +2446,19 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>4797500</v>
+        <v>4541300</v>
       </c>
       <c r="E72" s="3">
-        <v>4990500</v>
+        <v>4723900</v>
       </c>
       <c r="F72" s="3">
-        <v>5270300</v>
+        <v>4988800</v>
       </c>
       <c r="G72" s="3">
-        <v>5251500</v>
+        <v>4971000</v>
       </c>
       <c r="H72" s="3">
-        <v>4726700</v>
+        <v>4474200</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>3</v>
@@ -2566,19 +2566,19 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>6629900</v>
+        <v>6275700</v>
       </c>
       <c r="E76" s="3">
-        <v>6551700</v>
+        <v>6201700</v>
       </c>
       <c r="F76" s="3">
-        <v>6505000</v>
+        <v>6157600</v>
       </c>
       <c r="G76" s="3">
-        <v>6225700</v>
+        <v>5893100</v>
       </c>
       <c r="H76" s="3">
-        <v>5780900</v>
+        <v>5472100</v>
       </c>
       <c r="I76" s="3" t="s">
         <v>3</v>
@@ -2661,22 +2661,22 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>295700</v>
+        <v>279900</v>
       </c>
       <c r="E81" s="3">
-        <v>579900</v>
+        <v>548900</v>
       </c>
       <c r="F81" s="3">
-        <v>738900</v>
+        <v>699500</v>
       </c>
       <c r="G81" s="3">
-        <v>850200</v>
+        <v>804800</v>
       </c>
       <c r="H81" s="3">
-        <v>999000</v>
+        <v>945600</v>
       </c>
       <c r="I81" s="3">
-        <v>1035900</v>
+        <v>980600</v>
       </c>
       <c r="J81" s="3" t="s">
         <v>3</v>
@@ -2705,19 +2705,19 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>603900</v>
+        <v>571600</v>
       </c>
       <c r="E83" s="3">
-        <v>604800</v>
+        <v>572500</v>
       </c>
       <c r="F83" s="3">
-        <v>588700</v>
+        <v>557200</v>
       </c>
       <c r="G83" s="3">
-        <v>580200</v>
+        <v>549200</v>
       </c>
       <c r="H83" s="3">
-        <v>561900</v>
+        <v>531900</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>3</v>
@@ -2885,19 +2885,19 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1364700</v>
+        <v>1291800</v>
       </c>
       <c r="E89" s="3">
-        <v>882300</v>
+        <v>835200</v>
       </c>
       <c r="F89" s="3">
-        <v>1183000</v>
+        <v>1119800</v>
       </c>
       <c r="G89" s="3">
-        <v>1447200</v>
+        <v>1369900</v>
       </c>
       <c r="H89" s="3">
-        <v>1648100</v>
+        <v>1560100</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>3</v>
@@ -2929,19 +2929,19 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-365100</v>
+        <v>-345600</v>
       </c>
       <c r="E91" s="3">
-        <v>-441600</v>
+        <v>-418000</v>
       </c>
       <c r="F91" s="3">
-        <v>-404100</v>
+        <v>-382500</v>
       </c>
       <c r="G91" s="3">
-        <v>-400300</v>
+        <v>-378900</v>
       </c>
       <c r="H91" s="3">
-        <v>-565900</v>
+        <v>-535700</v>
       </c>
       <c r="I91" s="3" t="s">
         <v>3</v>
@@ -3019,19 +3019,19 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-736700</v>
+        <v>-697300</v>
       </c>
       <c r="E94" s="3">
-        <v>-504900</v>
+        <v>-477900</v>
       </c>
       <c r="F94" s="3">
-        <v>-453100</v>
+        <v>-428900</v>
       </c>
       <c r="G94" s="3">
-        <v>-417500</v>
+        <v>-395200</v>
       </c>
       <c r="H94" s="3">
-        <v>-635400</v>
+        <v>-601400</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>3</v>
@@ -3063,19 +3063,19 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-467300</v>
+        <v>-442400</v>
       </c>
       <c r="E96" s="3">
-        <v>-464600</v>
+        <v>-439800</v>
       </c>
       <c r="F96" s="3">
-        <v>-457400</v>
+        <v>-432900</v>
       </c>
       <c r="G96" s="3">
-        <v>-438000</v>
+        <v>-414600</v>
       </c>
       <c r="H96" s="3">
-        <v>-407900</v>
+        <v>-386100</v>
       </c>
       <c r="I96" s="3">
         <v>0</v>
@@ -3183,19 +3183,19 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-539100</v>
+        <v>-510300</v>
       </c>
       <c r="E100" s="3">
-        <v>-939000</v>
+        <v>-888800</v>
       </c>
       <c r="F100" s="3">
-        <v>-954200</v>
+        <v>-903200</v>
       </c>
       <c r="G100" s="3">
-        <v>-586800</v>
+        <v>-555500</v>
       </c>
       <c r="H100" s="3">
-        <v>-850400</v>
+        <v>-804900</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>3</v>
@@ -3213,19 +3213,19 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>68900</v>
+        <v>65200</v>
       </c>
       <c r="E101" s="3">
-        <v>104400</v>
+        <v>98900</v>
       </c>
       <c r="F101" s="3">
-        <v>109000</v>
+        <v>103200</v>
       </c>
       <c r="G101" s="3">
-        <v>-14900</v>
+        <v>-14100</v>
       </c>
       <c r="H101" s="3">
-        <v>-2600</v>
+        <v>-2500</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>3</v>
@@ -3243,19 +3243,19 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>157800</v>
+        <v>149400</v>
       </c>
       <c r="E102" s="3">
-        <v>-457100</v>
+        <v>-432700</v>
       </c>
       <c r="F102" s="3">
-        <v>-115300</v>
+        <v>-109100</v>
       </c>
       <c r="G102" s="3">
-        <v>428000</v>
+        <v>405100</v>
       </c>
       <c r="H102" s="3">
-        <v>159800</v>
+        <v>151200</v>
       </c>
       <c r="I102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/KAOOY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/KAOOY_YR_FIN.xlsx
@@ -712,22 +712,22 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>9777900</v>
+        <v>10881300</v>
       </c>
       <c r="E8" s="3">
-        <v>9895800</v>
+        <v>11012500</v>
       </c>
       <c r="F8" s="3">
-        <v>9051700</v>
+        <v>10073300</v>
       </c>
       <c r="G8" s="3">
-        <v>8817100</v>
+        <v>9812200</v>
       </c>
       <c r="H8" s="3">
-        <v>9584300</v>
+        <v>10665900</v>
       </c>
       <c r="I8" s="3">
-        <v>9621100</v>
+        <v>10706800</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>3</v>
@@ -742,22 +742,22 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>6202300</v>
+        <v>6902300</v>
       </c>
       <c r="E9" s="3">
-        <v>6397300</v>
+        <v>7119300</v>
       </c>
       <c r="F9" s="3">
-        <v>5394800</v>
+        <v>6003600</v>
       </c>
       <c r="G9" s="3">
-        <v>5048500</v>
+        <v>5618300</v>
       </c>
       <c r="H9" s="3">
-        <v>5414900</v>
+        <v>6025900</v>
       </c>
       <c r="I9" s="3">
-        <v>5448400</v>
+        <v>6063300</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>3</v>
@@ -772,22 +772,22 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>3575500</v>
+        <v>3979000</v>
       </c>
       <c r="E10" s="3">
-        <v>3498400</v>
+        <v>3893200</v>
       </c>
       <c r="F10" s="3">
-        <v>3657000</v>
+        <v>4069700</v>
       </c>
       <c r="G10" s="3">
-        <v>3768600</v>
+        <v>4193900</v>
       </c>
       <c r="H10" s="3">
-        <v>4169400</v>
+        <v>4640000</v>
       </c>
       <c r="I10" s="3">
-        <v>4172600</v>
+        <v>4643500</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>3</v>
@@ -816,22 +816,22 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>399200</v>
+        <v>444300</v>
       </c>
       <c r="E12" s="3">
-        <v>386600</v>
+        <v>430300</v>
       </c>
       <c r="F12" s="3">
-        <v>376400</v>
+        <v>418900</v>
       </c>
       <c r="G12" s="3">
-        <v>373300</v>
+        <v>415400</v>
       </c>
       <c r="H12" s="3">
-        <v>377300</v>
+        <v>419900</v>
       </c>
       <c r="I12" s="3">
-        <v>368000</v>
+        <v>409500</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>3</v>
@@ -876,22 +876,22 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>138500</v>
+        <v>154100</v>
       </c>
       <c r="E14" s="3">
         <v>200</v>
       </c>
       <c r="F14" s="3">
-        <v>29000</v>
+        <v>32300</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H14" s="3">
-        <v>4800</v>
+        <v>5300</v>
       </c>
       <c r="I14" s="3">
-        <v>9700</v>
+        <v>10800</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
@@ -906,22 +906,22 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>177500</v>
+        <v>197500</v>
       </c>
       <c r="E15" s="3">
-        <v>169100</v>
+        <v>188200</v>
       </c>
       <c r="F15" s="3">
-        <v>167100</v>
+        <v>185900</v>
       </c>
       <c r="G15" s="3">
-        <v>173700</v>
+        <v>193200</v>
       </c>
       <c r="H15" s="3">
-        <v>170500</v>
+        <v>189700</v>
       </c>
       <c r="I15" s="3">
-        <v>102400</v>
+        <v>113900</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>3</v>
@@ -947,22 +947,22 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>9394800</v>
+        <v>10455100</v>
       </c>
       <c r="E17" s="3">
-        <v>9193500</v>
+        <v>10231000</v>
       </c>
       <c r="F17" s="3">
-        <v>8136100</v>
+        <v>9054300</v>
       </c>
       <c r="G17" s="3">
-        <v>7697000</v>
+        <v>8565700</v>
       </c>
       <c r="H17" s="3">
-        <v>8233500</v>
+        <v>9162700</v>
       </c>
       <c r="I17" s="3">
-        <v>8295900</v>
+        <v>9232200</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>3</v>
@@ -977,22 +977,22 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>383000</v>
+        <v>426200</v>
       </c>
       <c r="E18" s="3">
-        <v>702300</v>
+        <v>781500</v>
       </c>
       <c r="F18" s="3">
-        <v>915600</v>
+        <v>1018900</v>
       </c>
       <c r="G18" s="3">
-        <v>1120100</v>
+        <v>1246500</v>
       </c>
       <c r="H18" s="3">
-        <v>1350800</v>
+        <v>1503200</v>
       </c>
       <c r="I18" s="3">
-        <v>1325100</v>
+        <v>1474700</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>3</v>
@@ -1021,22 +1021,22 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>45900</v>
+        <v>51100</v>
       </c>
       <c r="E20" s="3">
-        <v>51900</v>
+        <v>57700</v>
       </c>
       <c r="F20" s="3">
-        <v>57300</v>
+        <v>63800</v>
       </c>
       <c r="G20" s="3">
-        <v>16800</v>
+        <v>18700</v>
       </c>
       <c r="H20" s="3">
-        <v>16500</v>
+        <v>18400</v>
       </c>
       <c r="I20" s="3">
-        <v>9400</v>
+        <v>10500</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>3</v>
@@ -1051,19 +1051,19 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>999600</v>
+        <v>1109000</v>
       </c>
       <c r="E21" s="3">
-        <v>1325800</v>
+        <v>1471900</v>
       </c>
       <c r="F21" s="3">
-        <v>1529200</v>
+        <v>1698400</v>
       </c>
       <c r="G21" s="3">
-        <v>1685200</v>
+        <v>1872000</v>
       </c>
       <c r="H21" s="3">
-        <v>1898400</v>
+        <v>2109400</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>3</v>
@@ -1081,22 +1081,22 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>21600</v>
+        <v>24000</v>
       </c>
       <c r="E22" s="3">
-        <v>15000</v>
+        <v>16700</v>
       </c>
       <c r="F22" s="3">
-        <v>15900</v>
+        <v>17700</v>
       </c>
       <c r="G22" s="3">
-        <v>26900</v>
+        <v>30000</v>
       </c>
       <c r="H22" s="3">
-        <v>23400</v>
+        <v>26000</v>
       </c>
       <c r="I22" s="3">
-        <v>12300</v>
+        <v>13700</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>3</v>
@@ -1111,22 +1111,22 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>407300</v>
+        <v>453300</v>
       </c>
       <c r="E23" s="3">
-        <v>739100</v>
+        <v>822500</v>
       </c>
       <c r="F23" s="3">
-        <v>957000</v>
+        <v>1065000</v>
       </c>
       <c r="G23" s="3">
-        <v>1109900</v>
+        <v>1235200</v>
       </c>
       <c r="H23" s="3">
-        <v>1343900</v>
+        <v>1495600</v>
       </c>
       <c r="I23" s="3">
-        <v>1322300</v>
+        <v>1471500</v>
       </c>
       <c r="J23" s="3" t="s">
         <v>3</v>
@@ -1141,22 +1141,22 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>111400</v>
+        <v>123900</v>
       </c>
       <c r="E24" s="3">
-        <v>177500</v>
+        <v>197600</v>
       </c>
       <c r="F24" s="3">
-        <v>244900</v>
+        <v>272600</v>
       </c>
       <c r="G24" s="3">
-        <v>291900</v>
+        <v>324900</v>
       </c>
       <c r="H24" s="3">
-        <v>384200</v>
+        <v>427500</v>
       </c>
       <c r="I24" s="3">
-        <v>328800</v>
+        <v>365900</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
@@ -1201,22 +1201,22 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>295900</v>
+        <v>329300</v>
       </c>
       <c r="E26" s="3">
-        <v>561600</v>
+        <v>624900</v>
       </c>
       <c r="F26" s="3">
-        <v>712100</v>
+        <v>792400</v>
       </c>
       <c r="G26" s="3">
-        <v>818000</v>
+        <v>910300</v>
       </c>
       <c r="H26" s="3">
-        <v>959700</v>
+        <v>1068000</v>
       </c>
       <c r="I26" s="3">
-        <v>993500</v>
+        <v>1105600</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>3</v>
@@ -1231,22 +1231,22 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>281400</v>
+        <v>313100</v>
       </c>
       <c r="E27" s="3">
-        <v>550700</v>
+        <v>612900</v>
       </c>
       <c r="F27" s="3">
-        <v>700700</v>
+        <v>779800</v>
       </c>
       <c r="G27" s="3">
-        <v>805700</v>
+        <v>896600</v>
       </c>
       <c r="H27" s="3">
-        <v>946100</v>
+        <v>1052900</v>
       </c>
       <c r="I27" s="3">
-        <v>983000</v>
+        <v>1094000</v>
       </c>
       <c r="J27" s="3" t="s">
         <v>3</v>
@@ -1291,22 +1291,22 @@
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>-1500</v>
+        <v>-1600</v>
       </c>
       <c r="E29" s="3">
-        <v>-1800</v>
+        <v>-2000</v>
       </c>
       <c r="F29" s="3">
-        <v>-1300</v>
+        <v>-1400</v>
       </c>
       <c r="G29" s="3">
-        <v>-900</v>
+        <v>-1000</v>
       </c>
       <c r="H29" s="3">
-        <v>-500</v>
+        <v>-600</v>
       </c>
       <c r="I29" s="3">
-        <v>-2500</v>
+        <v>-2700</v>
       </c>
       <c r="J29" s="3" t="s">
         <v>3</v>
@@ -1381,22 +1381,22 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-45900</v>
+        <v>-51100</v>
       </c>
       <c r="E32" s="3">
-        <v>-51900</v>
+        <v>-57700</v>
       </c>
       <c r="F32" s="3">
-        <v>-57300</v>
+        <v>-63800</v>
       </c>
       <c r="G32" s="3">
-        <v>-16800</v>
+        <v>-18700</v>
       </c>
       <c r="H32" s="3">
-        <v>-16500</v>
+        <v>-18400</v>
       </c>
       <c r="I32" s="3">
-        <v>-9400</v>
+        <v>-10500</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>3</v>
@@ -1411,22 +1411,22 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>279900</v>
+        <v>311500</v>
       </c>
       <c r="E33" s="3">
-        <v>548900</v>
+        <v>610900</v>
       </c>
       <c r="F33" s="3">
-        <v>699500</v>
+        <v>778400</v>
       </c>
       <c r="G33" s="3">
-        <v>804800</v>
+        <v>895600</v>
       </c>
       <c r="H33" s="3">
-        <v>945600</v>
+        <v>1052300</v>
       </c>
       <c r="I33" s="3">
-        <v>980600</v>
+        <v>1091300</v>
       </c>
       <c r="J33" s="3" t="s">
         <v>3</v>
@@ -1471,22 +1471,22 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>279900</v>
+        <v>311500</v>
       </c>
       <c r="E35" s="3">
-        <v>548900</v>
+        <v>610900</v>
       </c>
       <c r="F35" s="3">
-        <v>699500</v>
+        <v>778400</v>
       </c>
       <c r="G35" s="3">
-        <v>804800</v>
+        <v>895600</v>
       </c>
       <c r="H35" s="3">
-        <v>945600</v>
+        <v>1052300</v>
       </c>
       <c r="I35" s="3">
-        <v>980600</v>
+        <v>1091300</v>
       </c>
       <c r="J35" s="3" t="s">
         <v>3</v>
@@ -1564,19 +1564,19 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1828900</v>
+        <v>2035300</v>
       </c>
       <c r="E41" s="3">
-        <v>1603000</v>
+        <v>1783900</v>
       </c>
       <c r="F41" s="3">
-        <v>2003800</v>
+        <v>2229900</v>
       </c>
       <c r="G41" s="3">
-        <v>2095000</v>
+        <v>2331500</v>
       </c>
       <c r="H41" s="3">
-        <v>1529800</v>
+        <v>1702400</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>3</v>
@@ -1594,19 +1594,19 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>74000</v>
+        <v>82300</v>
       </c>
       <c r="E42" s="3">
-        <v>131500</v>
+        <v>146300</v>
       </c>
       <c r="F42" s="3">
-        <v>179200</v>
+        <v>199500</v>
       </c>
       <c r="G42" s="3">
-        <v>204500</v>
+        <v>227600</v>
       </c>
       <c r="H42" s="3">
-        <v>406300</v>
+        <v>452200</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>3</v>
@@ -1624,19 +1624,19 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1474500</v>
+        <v>1641000</v>
       </c>
       <c r="E43" s="3">
-        <v>1497900</v>
+        <v>1666900</v>
       </c>
       <c r="F43" s="3">
-        <v>1395400</v>
+        <v>1552900</v>
       </c>
       <c r="G43" s="3">
-        <v>1289900</v>
+        <v>1435400</v>
       </c>
       <c r="H43" s="3">
-        <v>1348000</v>
+        <v>1500100</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>3</v>
@@ -1654,19 +1654,19 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1683100</v>
+        <v>1873100</v>
       </c>
       <c r="E44" s="3">
-        <v>1776100</v>
+        <v>1976500</v>
       </c>
       <c r="F44" s="3">
-        <v>1455100</v>
+        <v>1619300</v>
       </c>
       <c r="G44" s="3">
-        <v>1260900</v>
+        <v>1403300</v>
       </c>
       <c r="H44" s="3">
-        <v>1273900</v>
+        <v>1417700</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>3</v>
@@ -1684,19 +1684,19 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>152600</v>
+        <v>169800</v>
       </c>
       <c r="E45" s="3">
-        <v>141600</v>
+        <v>157600</v>
       </c>
       <c r="F45" s="3">
-        <v>133000</v>
+        <v>148000</v>
       </c>
       <c r="G45" s="3">
-        <v>115800</v>
+        <v>128900</v>
       </c>
       <c r="H45" s="3">
-        <v>144200</v>
+        <v>160500</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
@@ -1714,19 +1714,19 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>5213200</v>
+        <v>5801500</v>
       </c>
       <c r="E46" s="3">
-        <v>5150000</v>
+        <v>5731200</v>
       </c>
       <c r="F46" s="3">
-        <v>5166500</v>
+        <v>5749500</v>
       </c>
       <c r="G46" s="3">
-        <v>4966200</v>
+        <v>5526600</v>
       </c>
       <c r="H46" s="3">
-        <v>4702200</v>
+        <v>5232900</v>
       </c>
       <c r="I46" s="3" t="s">
         <v>3</v>
@@ -1744,19 +1744,19 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>246800</v>
+        <v>274700</v>
       </c>
       <c r="E47" s="3">
-        <v>232100</v>
+        <v>258300</v>
       </c>
       <c r="F47" s="3">
-        <v>214600</v>
+        <v>238800</v>
       </c>
       <c r="G47" s="3">
-        <v>205900</v>
+        <v>229100</v>
       </c>
       <c r="H47" s="3">
-        <v>219400</v>
+        <v>244200</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>3</v>
@@ -1774,19 +1774,19 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>3488700</v>
+        <v>3882400</v>
       </c>
       <c r="E48" s="3">
-        <v>3687300</v>
+        <v>4103500</v>
       </c>
       <c r="F48" s="3">
-        <v>3653600</v>
+        <v>4065900</v>
       </c>
       <c r="G48" s="3">
-        <v>3703300</v>
+        <v>4121200</v>
       </c>
       <c r="H48" s="3">
-        <v>3838500</v>
+        <v>4271700</v>
       </c>
       <c r="I48" s="3" t="s">
         <v>3</v>
@@ -1804,19 +1804,19 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1918100</v>
+        <v>2134600</v>
       </c>
       <c r="E49" s="3">
-        <v>1608000</v>
+        <v>1789500</v>
       </c>
       <c r="F49" s="3">
-        <v>1506500</v>
+        <v>1676600</v>
       </c>
       <c r="G49" s="3">
-        <v>1437300</v>
+        <v>1599500</v>
       </c>
       <c r="H49" s="3">
-        <v>1451300</v>
+        <v>1615100</v>
       </c>
       <c r="I49" s="3" t="s">
         <v>3</v>
@@ -1894,19 +1894,19 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>424200</v>
+        <v>472100</v>
       </c>
       <c r="E52" s="3">
-        <v>336600</v>
+        <v>374600</v>
       </c>
       <c r="F52" s="3">
-        <v>330300</v>
+        <v>367600</v>
       </c>
       <c r="G52" s="3">
-        <v>314000</v>
+        <v>349400</v>
       </c>
       <c r="H52" s="3">
-        <v>340500</v>
+        <v>378900</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>3</v>
@@ -1954,19 +1954,19 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>11291000</v>
+        <v>12565200</v>
       </c>
       <c r="E54" s="3">
-        <v>11014100</v>
+        <v>12257100</v>
       </c>
       <c r="F54" s="3">
-        <v>10871600</v>
+        <v>12098400</v>
       </c>
       <c r="G54" s="3">
-        <v>10626600</v>
+        <v>11825900</v>
       </c>
       <c r="H54" s="3">
-        <v>10552000</v>
+        <v>11742800</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>3</v>
@@ -2012,19 +2012,19 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1033200</v>
+        <v>1149800</v>
       </c>
       <c r="E57" s="3">
-        <v>1098500</v>
+        <v>1222400</v>
       </c>
       <c r="F57" s="3">
-        <v>995200</v>
+        <v>1107500</v>
       </c>
       <c r="G57" s="3">
-        <v>878400</v>
+        <v>977500</v>
       </c>
       <c r="H57" s="3">
-        <v>924200</v>
+        <v>1028500</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>3</v>
@@ -2042,19 +2042,19 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>210900</v>
+        <v>234700</v>
       </c>
       <c r="E58" s="3">
-        <v>543000</v>
+        <v>604300</v>
       </c>
       <c r="F58" s="3">
-        <v>166400</v>
+        <v>185200</v>
       </c>
       <c r="G58" s="3">
+        <v>356800</v>
+      </c>
+      <c r="H58" s="3">
         <v>320600</v>
-      </c>
-      <c r="H58" s="3">
-        <v>288100</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>3</v>
@@ -2072,19 +2072,19 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1690300</v>
+        <v>1881100</v>
       </c>
       <c r="E59" s="3">
-        <v>1463200</v>
+        <v>1628300</v>
       </c>
       <c r="F59" s="3">
-        <v>1530100</v>
+        <v>1702800</v>
       </c>
       <c r="G59" s="3">
-        <v>1515100</v>
+        <v>1686100</v>
       </c>
       <c r="H59" s="3">
-        <v>1547200</v>
+        <v>1721800</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>3</v>
@@ -2102,19 +2102,19 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>2934400</v>
+        <v>3265500</v>
       </c>
       <c r="E60" s="3">
-        <v>3104700</v>
+        <v>3455000</v>
       </c>
       <c r="F60" s="3">
-        <v>2691700</v>
+        <v>2995500</v>
       </c>
       <c r="G60" s="3">
-        <v>2714100</v>
+        <v>3020400</v>
       </c>
       <c r="H60" s="3">
-        <v>2759500</v>
+        <v>3070900</v>
       </c>
       <c r="I60" s="3" t="s">
         <v>3</v>
@@ -2132,19 +2132,19 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1454700</v>
+        <v>1618900</v>
       </c>
       <c r="E61" s="3">
-        <v>1134200</v>
+        <v>1262200</v>
       </c>
       <c r="F61" s="3">
-        <v>1547800</v>
+        <v>1722400</v>
       </c>
       <c r="G61" s="3">
-        <v>1428800</v>
+        <v>1590100</v>
       </c>
       <c r="H61" s="3">
-        <v>1550800</v>
+        <v>1725800</v>
       </c>
       <c r="I61" s="3">
         <v>0</v>
@@ -2162,19 +2162,19 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>445000</v>
+        <v>495300</v>
       </c>
       <c r="E62" s="3">
-        <v>424700</v>
+        <v>472600</v>
       </c>
       <c r="F62" s="3">
-        <v>355000</v>
+        <v>395000</v>
       </c>
       <c r="G62" s="3">
-        <v>498000</v>
+        <v>554300</v>
       </c>
       <c r="H62" s="3">
-        <v>682000</v>
+        <v>759000</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
@@ -2282,19 +2282,19 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>5015200</v>
+        <v>5581200</v>
       </c>
       <c r="E66" s="3">
-        <v>4812400</v>
+        <v>5355500</v>
       </c>
       <c r="F66" s="3">
-        <v>4714000</v>
+        <v>5246000</v>
       </c>
       <c r="G66" s="3">
-        <v>4733500</v>
+        <v>5267700</v>
       </c>
       <c r="H66" s="3">
-        <v>5079900</v>
+        <v>5653200</v>
       </c>
       <c r="I66" s="3" t="s">
         <v>3</v>
@@ -2446,19 +2446,19 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>4541300</v>
+        <v>5053800</v>
       </c>
       <c r="E72" s="3">
-        <v>4723900</v>
+        <v>5257100</v>
       </c>
       <c r="F72" s="3">
-        <v>4988800</v>
+        <v>5551800</v>
       </c>
       <c r="G72" s="3">
-        <v>4971000</v>
+        <v>5532000</v>
       </c>
       <c r="H72" s="3">
-        <v>4474200</v>
+        <v>4979100</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>3</v>
@@ -2566,19 +2566,19 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>6275700</v>
+        <v>6984000</v>
       </c>
       <c r="E76" s="3">
-        <v>6201700</v>
+        <v>6901600</v>
       </c>
       <c r="F76" s="3">
-        <v>6157600</v>
+        <v>6852500</v>
       </c>
       <c r="G76" s="3">
-        <v>5893100</v>
+        <v>6558200</v>
       </c>
       <c r="H76" s="3">
-        <v>5472100</v>
+        <v>6089600</v>
       </c>
       <c r="I76" s="3" t="s">
         <v>3</v>
@@ -2661,22 +2661,22 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>279900</v>
+        <v>311500</v>
       </c>
       <c r="E81" s="3">
-        <v>548900</v>
+        <v>610900</v>
       </c>
       <c r="F81" s="3">
-        <v>699500</v>
+        <v>778400</v>
       </c>
       <c r="G81" s="3">
-        <v>804800</v>
+        <v>895600</v>
       </c>
       <c r="H81" s="3">
-        <v>945600</v>
+        <v>1052300</v>
       </c>
       <c r="I81" s="3">
-        <v>980600</v>
+        <v>1091300</v>
       </c>
       <c r="J81" s="3" t="s">
         <v>3</v>
@@ -2705,19 +2705,19 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>571600</v>
+        <v>636100</v>
       </c>
       <c r="E83" s="3">
-        <v>572500</v>
+        <v>637100</v>
       </c>
       <c r="F83" s="3">
-        <v>557200</v>
+        <v>620100</v>
       </c>
       <c r="G83" s="3">
-        <v>549200</v>
+        <v>611200</v>
       </c>
       <c r="H83" s="3">
-        <v>531900</v>
+        <v>591900</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>3</v>
@@ -2885,19 +2885,19 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1291800</v>
+        <v>1437600</v>
       </c>
       <c r="E89" s="3">
-        <v>835200</v>
+        <v>929400</v>
       </c>
       <c r="F89" s="3">
-        <v>1119800</v>
+        <v>1246200</v>
       </c>
       <c r="G89" s="3">
-        <v>1369900</v>
+        <v>1524500</v>
       </c>
       <c r="H89" s="3">
-        <v>1560100</v>
+        <v>1736100</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>3</v>
@@ -2929,19 +2929,19 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-345600</v>
+        <v>-384600</v>
       </c>
       <c r="E91" s="3">
-        <v>-418000</v>
+        <v>-465200</v>
       </c>
       <c r="F91" s="3">
-        <v>-382500</v>
+        <v>-425700</v>
       </c>
       <c r="G91" s="3">
-        <v>-378900</v>
+        <v>-421700</v>
       </c>
       <c r="H91" s="3">
-        <v>-535700</v>
+        <v>-596100</v>
       </c>
       <c r="I91" s="3" t="s">
         <v>3</v>
@@ -3019,19 +3019,19 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-697300</v>
+        <v>-776000</v>
       </c>
       <c r="E94" s="3">
-        <v>-477900</v>
+        <v>-531900</v>
       </c>
       <c r="F94" s="3">
-        <v>-428900</v>
+        <v>-477300</v>
       </c>
       <c r="G94" s="3">
-        <v>-395200</v>
+        <v>-439800</v>
       </c>
       <c r="H94" s="3">
-        <v>-601400</v>
+        <v>-669300</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>3</v>
@@ -3063,19 +3063,19 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-442400</v>
+        <v>-492300</v>
       </c>
       <c r="E96" s="3">
-        <v>-439800</v>
+        <v>-489400</v>
       </c>
       <c r="F96" s="3">
-        <v>-432900</v>
+        <v>-481800</v>
       </c>
       <c r="G96" s="3">
-        <v>-414600</v>
+        <v>-461400</v>
       </c>
       <c r="H96" s="3">
-        <v>-386100</v>
+        <v>-429600</v>
       </c>
       <c r="I96" s="3">
         <v>0</v>
@@ -3183,19 +3183,19 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-510300</v>
+        <v>-567900</v>
       </c>
       <c r="E100" s="3">
-        <v>-888800</v>
+        <v>-989100</v>
       </c>
       <c r="F100" s="3">
-        <v>-903200</v>
+        <v>-1005200</v>
       </c>
       <c r="G100" s="3">
-        <v>-555500</v>
+        <v>-618200</v>
       </c>
       <c r="H100" s="3">
-        <v>-804900</v>
+        <v>-895800</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>3</v>
@@ -3213,19 +3213,19 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>65200</v>
+        <v>72600</v>
       </c>
       <c r="E101" s="3">
-        <v>98900</v>
+        <v>110000</v>
       </c>
       <c r="F101" s="3">
-        <v>103200</v>
+        <v>114800</v>
       </c>
       <c r="G101" s="3">
-        <v>-14100</v>
+        <v>-15700</v>
       </c>
       <c r="H101" s="3">
-        <v>-2500</v>
+        <v>-2800</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>3</v>
@@ -3243,19 +3243,19 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>149400</v>
+        <v>166200</v>
       </c>
       <c r="E102" s="3">
-        <v>-432700</v>
+        <v>-481500</v>
       </c>
       <c r="F102" s="3">
-        <v>-109100</v>
+        <v>-121500</v>
       </c>
       <c r="G102" s="3">
-        <v>405100</v>
+        <v>450800</v>
       </c>
       <c r="H102" s="3">
-        <v>151200</v>
+        <v>168300</v>
       </c>
       <c r="I102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/KAOOY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/KAOOY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="92">
   <si>
     <t>KAOOY</t>
   </si>
@@ -662,8 +662,8 @@
     <col min="1" max="1" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
@@ -699,8 +699,8 @@
       <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>3</v>
+      <c r="J7" s="2">
+        <v>43100</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>3</v>
@@ -712,25 +712,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>10881300</v>
+        <v>10872300</v>
       </c>
       <c r="E8" s="3">
-        <v>11012500</v>
+        <v>11761800</v>
       </c>
       <c r="F8" s="3">
-        <v>10073300</v>
+        <v>12322300</v>
       </c>
       <c r="G8" s="3">
-        <v>9812200</v>
+        <v>13390500</v>
       </c>
       <c r="H8" s="3">
-        <v>10665900</v>
+        <v>13823000</v>
       </c>
       <c r="I8" s="3">
-        <v>10706800</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
+        <v>13744800</v>
+      </c>
+      <c r="J8" s="3">
+        <v>13223400</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
@@ -742,25 +742,25 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>6902300</v>
+        <v>6896600</v>
       </c>
       <c r="E9" s="3">
-        <v>7119300</v>
+        <v>7603700</v>
       </c>
       <c r="F9" s="3">
-        <v>6003600</v>
+        <v>7344000</v>
       </c>
       <c r="G9" s="3">
-        <v>5618300</v>
+        <v>7667200</v>
       </c>
       <c r="H9" s="3">
-        <v>6025900</v>
+        <v>7809600</v>
       </c>
       <c r="I9" s="3">
-        <v>6063300</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
+        <v>7783700</v>
+      </c>
+      <c r="J9" s="3">
+        <v>7405400</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
@@ -772,25 +772,25 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>3979000</v>
+        <v>3975700</v>
       </c>
       <c r="E10" s="3">
-        <v>3893200</v>
+        <v>4158100</v>
       </c>
       <c r="F10" s="3">
-        <v>4069700</v>
+        <v>4978300</v>
       </c>
       <c r="G10" s="3">
-        <v>4193900</v>
+        <v>5723400</v>
       </c>
       <c r="H10" s="3">
-        <v>4640000</v>
+        <v>6013400</v>
       </c>
       <c r="I10" s="3">
-        <v>4643500</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+        <v>5961100</v>
+      </c>
+      <c r="J10" s="3">
+        <v>5818000</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -816,25 +816,25 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>444300</v>
+        <v>443900</v>
       </c>
       <c r="E12" s="3">
-        <v>430300</v>
+        <v>459500</v>
       </c>
       <c r="F12" s="3">
-        <v>418900</v>
+        <v>512400</v>
       </c>
       <c r="G12" s="3">
-        <v>415400</v>
+        <v>566900</v>
       </c>
       <c r="H12" s="3">
-        <v>419900</v>
+        <v>544200</v>
       </c>
       <c r="I12" s="3">
-        <v>409500</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>3</v>
+        <v>525700</v>
+      </c>
+      <c r="J12" s="3">
+        <v>503400</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>3</v>
@@ -876,25 +876,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>154100</v>
+        <v>285000</v>
       </c>
       <c r="E14" s="3">
-        <v>200</v>
+        <v>27700</v>
       </c>
       <c r="F14" s="3">
-        <v>32300</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
+        <v>80200</v>
+      </c>
+      <c r="G14" s="3">
+        <v>32400</v>
       </c>
       <c r="H14" s="3">
-        <v>5300</v>
+        <v>40000</v>
       </c>
       <c r="I14" s="3">
-        <v>10800</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
+        <v>57300</v>
+      </c>
+      <c r="J14" s="3">
+        <v>33100</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
@@ -906,25 +906,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>197500</v>
+        <v>197400</v>
       </c>
       <c r="E15" s="3">
-        <v>188200</v>
+        <v>201000</v>
       </c>
       <c r="F15" s="3">
-        <v>185900</v>
+        <v>227400</v>
       </c>
       <c r="G15" s="3">
-        <v>193200</v>
+        <v>263700</v>
       </c>
       <c r="H15" s="3">
-        <v>189700</v>
+        <v>245900</v>
       </c>
       <c r="I15" s="3">
-        <v>113900</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>3</v>
+        <v>146300</v>
+      </c>
+      <c r="J15" s="3">
+        <v>121200</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>3</v>
@@ -947,25 +947,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>10455100</v>
+        <v>10161400</v>
       </c>
       <c r="E17" s="3">
-        <v>10231000</v>
+        <v>10899400</v>
       </c>
       <c r="F17" s="3">
-        <v>9054300</v>
+        <v>10995700</v>
       </c>
       <c r="G17" s="3">
-        <v>8565700</v>
+        <v>11657000</v>
       </c>
       <c r="H17" s="3">
-        <v>9162700</v>
+        <v>11834800</v>
       </c>
       <c r="I17" s="3">
-        <v>9232200</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
+        <v>11794400</v>
+      </c>
+      <c r="J17" s="3">
+        <v>11372100</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
@@ -977,25 +977,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>426200</v>
+        <v>710900</v>
       </c>
       <c r="E18" s="3">
-        <v>781500</v>
+        <v>862400</v>
       </c>
       <c r="F18" s="3">
-        <v>1018900</v>
+        <v>1326600</v>
       </c>
       <c r="G18" s="3">
-        <v>1246500</v>
+        <v>1733500</v>
       </c>
       <c r="H18" s="3">
-        <v>1503200</v>
+        <v>1988200</v>
       </c>
       <c r="I18" s="3">
-        <v>1474700</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
+        <v>1950400</v>
+      </c>
+      <c r="J18" s="3">
+        <v>1851300</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
@@ -1021,25 +1021,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>51100</v>
+        <v>-25300</v>
       </c>
       <c r="E20" s="3">
-        <v>57700</v>
+        <v>-44800</v>
       </c>
       <c r="F20" s="3">
-        <v>63800</v>
+        <v>-66200</v>
       </c>
       <c r="G20" s="3">
-        <v>18700</v>
+        <v>900</v>
       </c>
       <c r="H20" s="3">
-        <v>18400</v>
+        <v>-6200</v>
       </c>
       <c r="I20" s="3">
-        <v>10500</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
+        <v>1200</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-3000</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
@@ -1051,25 +1051,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1109000</v>
+        <v>933600</v>
       </c>
       <c r="E21" s="3">
-        <v>1471900</v>
+        <v>1108200</v>
       </c>
       <c r="F21" s="3">
-        <v>1698400</v>
+        <v>1620200</v>
       </c>
       <c r="G21" s="3">
-        <v>1872000</v>
+        <v>1996300</v>
       </c>
       <c r="H21" s="3">
-        <v>2109400</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+        <v>2240400</v>
+      </c>
+      <c r="I21" s="3">
+        <v>2095500</v>
+      </c>
+      <c r="J21" s="3">
+        <v>1975500</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1084,22 +1084,22 @@
         <v>24000</v>
       </c>
       <c r="E22" s="3">
-        <v>16700</v>
+        <v>17900</v>
       </c>
       <c r="F22" s="3">
-        <v>17700</v>
+        <v>21600</v>
       </c>
       <c r="G22" s="3">
-        <v>30000</v>
+        <v>29900</v>
       </c>
       <c r="H22" s="3">
-        <v>26000</v>
+        <v>33700</v>
       </c>
       <c r="I22" s="3">
-        <v>13700</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
+        <v>17600</v>
+      </c>
+      <c r="J22" s="3">
+        <v>19200</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
@@ -1111,25 +1111,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>453300</v>
+        <v>452900</v>
       </c>
       <c r="E23" s="3">
-        <v>822500</v>
+        <v>878500</v>
       </c>
       <c r="F23" s="3">
-        <v>1065000</v>
+        <v>1302800</v>
       </c>
       <c r="G23" s="3">
-        <v>1235200</v>
+        <v>1685700</v>
       </c>
       <c r="H23" s="3">
-        <v>1495600</v>
+        <v>1938300</v>
       </c>
       <c r="I23" s="3">
-        <v>1471500</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
+        <v>1889000</v>
+      </c>
+      <c r="J23" s="3">
+        <v>1813700</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>3</v>
@@ -1141,25 +1141,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>123900</v>
+        <v>125500</v>
       </c>
       <c r="E24" s="3">
-        <v>197600</v>
+        <v>213100</v>
       </c>
       <c r="F24" s="3">
-        <v>272600</v>
+        <v>335100</v>
       </c>
       <c r="G24" s="3">
-        <v>324900</v>
+        <v>444800</v>
       </c>
       <c r="H24" s="3">
-        <v>427500</v>
+        <v>554800</v>
       </c>
       <c r="I24" s="3">
-        <v>365900</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
+        <v>473200</v>
+      </c>
+      <c r="J24" s="3">
+        <v>494400</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
@@ -1201,25 +1201,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>329300</v>
+        <v>327400</v>
       </c>
       <c r="E26" s="3">
-        <v>624900</v>
+        <v>665400</v>
       </c>
       <c r="F26" s="3">
-        <v>792400</v>
+        <v>967700</v>
       </c>
       <c r="G26" s="3">
-        <v>910300</v>
+        <v>1240900</v>
       </c>
       <c r="H26" s="3">
-        <v>1068000</v>
+        <v>1383400</v>
       </c>
       <c r="I26" s="3">
-        <v>1105600</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
+        <v>1415800</v>
+      </c>
+      <c r="J26" s="3">
+        <v>1319400</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
@@ -1231,25 +1231,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>313100</v>
+        <v>311200</v>
       </c>
       <c r="E27" s="3">
-        <v>612900</v>
+        <v>652400</v>
       </c>
       <c r="F27" s="3">
-        <v>779800</v>
+        <v>952200</v>
       </c>
       <c r="G27" s="3">
-        <v>896600</v>
+        <v>1222200</v>
       </c>
       <c r="H27" s="3">
-        <v>1052900</v>
+        <v>1363800</v>
       </c>
       <c r="I27" s="3">
-        <v>1094000</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
+        <v>1400900</v>
+      </c>
+      <c r="J27" s="3">
+        <v>1305200</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
@@ -1291,25 +1291,25 @@
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>-1600</v>
+        <v>0</v>
       </c>
       <c r="E29" s="3">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="F29" s="3">
-        <v>-1400</v>
+        <v>0</v>
       </c>
       <c r="G29" s="3">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>3</v>
@@ -1381,25 +1381,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-51100</v>
+        <v>25300</v>
       </c>
       <c r="E32" s="3">
-        <v>-57700</v>
+        <v>44800</v>
       </c>
       <c r="F32" s="3">
-        <v>-63800</v>
+        <v>66200</v>
       </c>
       <c r="G32" s="3">
-        <v>-18700</v>
+        <v>-900</v>
       </c>
       <c r="H32" s="3">
-        <v>-18400</v>
+        <v>6200</v>
       </c>
       <c r="I32" s="3">
-        <v>-10500</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
+        <v>-1200</v>
+      </c>
+      <c r="J32" s="3">
+        <v>3000</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
@@ -1411,25 +1411,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>311500</v>
+        <v>311200</v>
       </c>
       <c r="E33" s="3">
-        <v>610900</v>
+        <v>652400</v>
       </c>
       <c r="F33" s="3">
-        <v>778400</v>
+        <v>952200</v>
       </c>
       <c r="G33" s="3">
-        <v>895600</v>
+        <v>1222200</v>
       </c>
       <c r="H33" s="3">
-        <v>1052300</v>
+        <v>1363800</v>
       </c>
       <c r="I33" s="3">
-        <v>1091300</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
+        <v>1400900</v>
+      </c>
+      <c r="J33" s="3">
+        <v>1305200</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
@@ -1471,25 +1471,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>311500</v>
+        <v>311200</v>
       </c>
       <c r="E35" s="3">
-        <v>610900</v>
+        <v>652400</v>
       </c>
       <c r="F35" s="3">
-        <v>778400</v>
+        <v>952200</v>
       </c>
       <c r="G35" s="3">
-        <v>895600</v>
+        <v>1222200</v>
       </c>
       <c r="H35" s="3">
-        <v>1052300</v>
+        <v>1363800</v>
       </c>
       <c r="I35" s="3">
-        <v>1091300</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
+        <v>1400900</v>
+      </c>
+      <c r="J35" s="3">
+        <v>1305200</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
@@ -1523,8 +1523,8 @@
       <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2" t="s">
-        <v>3</v>
+      <c r="J38" s="2">
+        <v>43100</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>3</v>
@@ -1564,25 +1564,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>2035300</v>
+        <v>2069100</v>
       </c>
       <c r="E41" s="3">
-        <v>1783900</v>
+        <v>2034100</v>
       </c>
       <c r="F41" s="3">
-        <v>2229900</v>
+        <v>2918800</v>
       </c>
       <c r="G41" s="3">
-        <v>2331500</v>
+        <v>3422000</v>
       </c>
       <c r="H41" s="3">
-        <v>1702400</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
+        <v>2665500</v>
+      </c>
+      <c r="I41" s="3">
+        <v>2424300</v>
+      </c>
+      <c r="J41" s="3">
+        <v>3045900</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
@@ -1594,25 +1594,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>82300</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>146300</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>199500</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>227600</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>452200</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>3</v>
@@ -1624,25 +1624,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1641000</v>
+        <v>1639600</v>
       </c>
       <c r="E43" s="3">
-        <v>1666900</v>
+        <v>1780300</v>
       </c>
       <c r="F43" s="3">
-        <v>1552900</v>
+        <v>1899600</v>
       </c>
       <c r="G43" s="3">
-        <v>1435400</v>
+        <v>1962500</v>
       </c>
       <c r="H43" s="3">
-        <v>1500100</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
+        <v>1948900</v>
+      </c>
+      <c r="I43" s="3">
+        <v>2078600</v>
+      </c>
+      <c r="J43" s="3">
+        <v>2017800</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
@@ -1654,25 +1654,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1873100</v>
+        <v>1871500</v>
       </c>
       <c r="E44" s="3">
-        <v>1976500</v>
+        <v>2111000</v>
       </c>
       <c r="F44" s="3">
-        <v>1619300</v>
+        <v>1980800</v>
       </c>
       <c r="G44" s="3">
-        <v>1403300</v>
+        <v>1915000</v>
       </c>
       <c r="H44" s="3">
-        <v>1417700</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
+        <v>1837300</v>
+      </c>
+      <c r="I44" s="3">
+        <v>1800800</v>
+      </c>
+      <c r="J44" s="3">
+        <v>1632900</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>3</v>
@@ -1684,25 +1684,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>169800</v>
+        <v>136100</v>
       </c>
       <c r="E45" s="3">
-        <v>157600</v>
+        <v>112600</v>
       </c>
       <c r="F45" s="3">
-        <v>148000</v>
+        <v>150900</v>
       </c>
       <c r="G45" s="3">
-        <v>128900</v>
+        <v>166100</v>
       </c>
       <c r="H45" s="3">
-        <v>160500</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
+        <v>251100</v>
+      </c>
+      <c r="I45" s="3">
+        <v>229400</v>
+      </c>
+      <c r="J45" s="3">
+        <v>226700</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
@@ -1714,25 +1714,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>5801500</v>
+        <v>5796700</v>
       </c>
       <c r="E46" s="3">
-        <v>5731200</v>
+        <v>6121100</v>
       </c>
       <c r="F46" s="3">
-        <v>5749500</v>
+        <v>7033200</v>
       </c>
       <c r="G46" s="3">
-        <v>5526600</v>
+        <v>7542100</v>
       </c>
       <c r="H46" s="3">
-        <v>5232900</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
+        <v>6781800</v>
+      </c>
+      <c r="I46" s="3">
+        <v>6620000</v>
+      </c>
+      <c r="J46" s="3">
+        <v>7008300</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
@@ -1744,25 +1744,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>274700</v>
+        <v>352300</v>
       </c>
       <c r="E47" s="3">
-        <v>258300</v>
+        <v>343600</v>
       </c>
       <c r="F47" s="3">
-        <v>238800</v>
+        <v>382700</v>
       </c>
       <c r="G47" s="3">
-        <v>229100</v>
+        <v>379800</v>
       </c>
       <c r="H47" s="3">
-        <v>244200</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
+        <v>367000</v>
+      </c>
+      <c r="I47" s="3">
+        <v>362300</v>
+      </c>
+      <c r="J47" s="3">
+        <v>405900</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
@@ -1774,25 +1774,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>3882400</v>
+        <v>3879200</v>
       </c>
       <c r="E48" s="3">
-        <v>4103500</v>
+        <v>4382700</v>
       </c>
       <c r="F48" s="3">
-        <v>4065900</v>
+        <v>4973700</v>
       </c>
       <c r="G48" s="3">
-        <v>4121200</v>
+        <v>5624200</v>
       </c>
       <c r="H48" s="3">
-        <v>4271700</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
+        <v>5536200</v>
+      </c>
+      <c r="I48" s="3">
+        <v>3818400</v>
+      </c>
+      <c r="J48" s="3">
+        <v>3514000</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
@@ -1804,25 +1804,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2134600</v>
+        <v>2132800</v>
       </c>
       <c r="E49" s="3">
-        <v>1789500</v>
+        <v>1911300</v>
       </c>
       <c r="F49" s="3">
-        <v>1676600</v>
+        <v>2050900</v>
       </c>
       <c r="G49" s="3">
-        <v>1599500</v>
+        <v>2182900</v>
       </c>
       <c r="H49" s="3">
-        <v>1615100</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
+        <v>2093100</v>
+      </c>
+      <c r="I49" s="3">
+        <v>2067500</v>
+      </c>
+      <c r="J49" s="3">
+        <v>1381100</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
@@ -1893,20 +1893,20 @@
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>472100</v>
-      </c>
-      <c r="E52" s="3">
-        <v>374600</v>
-      </c>
-      <c r="F52" s="3">
-        <v>367600</v>
-      </c>
-      <c r="G52" s="3">
-        <v>349400</v>
-      </c>
-      <c r="H52" s="3">
-        <v>378900</v>
+      <c r="D52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>3</v>
@@ -1954,25 +1954,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>12565200</v>
+        <v>12554800</v>
       </c>
       <c r="E54" s="3">
-        <v>12257100</v>
+        <v>13091000</v>
       </c>
       <c r="F54" s="3">
-        <v>12098400</v>
+        <v>14799700</v>
       </c>
       <c r="G54" s="3">
-        <v>11825900</v>
+        <v>16138600</v>
       </c>
       <c r="H54" s="3">
-        <v>11742800</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
+        <v>15218700</v>
+      </c>
+      <c r="I54" s="3">
+        <v>13316200</v>
+      </c>
+      <c r="J54" s="3">
+        <v>12672600</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
@@ -2012,25 +2012,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1149800</v>
+        <v>1670800</v>
       </c>
       <c r="E57" s="3">
-        <v>1222400</v>
+        <v>1848500</v>
       </c>
       <c r="F57" s="3">
-        <v>1107500</v>
+        <v>1989700</v>
       </c>
       <c r="G57" s="3">
-        <v>977500</v>
+        <v>2091400</v>
       </c>
       <c r="H57" s="3">
-        <v>1028500</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
+        <v>2045600</v>
+      </c>
+      <c r="I57" s="3">
+        <v>2055900</v>
+      </c>
+      <c r="J57" s="3">
+        <v>1996700</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
@@ -2042,25 +2042,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>234700</v>
+        <v>234500</v>
       </c>
       <c r="E58" s="3">
-        <v>604300</v>
+        <v>645400</v>
       </c>
       <c r="F58" s="3">
-        <v>185200</v>
+        <v>226600</v>
       </c>
       <c r="G58" s="3">
-        <v>356800</v>
+        <v>486900</v>
       </c>
       <c r="H58" s="3">
-        <v>320600</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+        <v>415500</v>
+      </c>
+      <c r="I58" s="3">
+        <v>375100</v>
+      </c>
+      <c r="J58" s="3">
+        <v>231000</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2072,25 +2072,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1881100</v>
+        <v>755800</v>
       </c>
       <c r="E59" s="3">
-        <v>1628300</v>
+        <v>526300</v>
       </c>
       <c r="F59" s="3">
-        <v>1702800</v>
+        <v>696500</v>
       </c>
       <c r="G59" s="3">
-        <v>1686100</v>
+        <v>759700</v>
       </c>
       <c r="H59" s="3">
-        <v>1721800</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
+        <v>778000</v>
+      </c>
+      <c r="I59" s="3">
+        <v>717600</v>
+      </c>
+      <c r="J59" s="3">
+        <v>725200</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
@@ -2102,25 +2102,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>3265500</v>
+        <v>3262800</v>
       </c>
       <c r="E60" s="3">
-        <v>3455000</v>
+        <v>3690100</v>
       </c>
       <c r="F60" s="3">
-        <v>2995500</v>
+        <v>3664300</v>
       </c>
       <c r="G60" s="3">
-        <v>3020400</v>
+        <v>4121900</v>
       </c>
       <c r="H60" s="3">
-        <v>3070900</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
+        <v>3979900</v>
+      </c>
+      <c r="I60" s="3">
+        <v>3926900</v>
+      </c>
+      <c r="J60" s="3">
+        <v>3743700</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
@@ -2132,25 +2132,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1618900</v>
+        <v>1617500</v>
       </c>
       <c r="E61" s="3">
-        <v>1262200</v>
+        <v>1348100</v>
       </c>
       <c r="F61" s="3">
-        <v>1722400</v>
+        <v>2107000</v>
       </c>
       <c r="G61" s="3">
-        <v>1590100</v>
+        <v>2169900</v>
       </c>
       <c r="H61" s="3">
-        <v>1725800</v>
+        <v>2236700</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>748300</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>867800</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -2162,25 +2162,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>495300</v>
+        <v>146300</v>
       </c>
       <c r="E62" s="3">
-        <v>472600</v>
+        <v>159000</v>
       </c>
       <c r="F62" s="3">
-        <v>395000</v>
+        <v>173400</v>
       </c>
       <c r="G62" s="3">
-        <v>554300</v>
+        <v>209500</v>
       </c>
       <c r="H62" s="3">
-        <v>759000</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
+        <v>207700</v>
+      </c>
+      <c r="I62" s="3">
+        <v>229000</v>
+      </c>
+      <c r="J62" s="3">
+        <v>208300</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
@@ -2282,25 +2282,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>5581200</v>
+        <v>5375200</v>
       </c>
       <c r="E66" s="3">
-        <v>5355500</v>
+        <v>5543000</v>
       </c>
       <c r="F66" s="3">
-        <v>5246000</v>
+        <v>6254500</v>
       </c>
       <c r="G66" s="3">
-        <v>5267700</v>
+        <v>7048200</v>
       </c>
       <c r="H66" s="3">
-        <v>5653200</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
+        <v>7200200</v>
+      </c>
+      <c r="I66" s="3">
+        <v>5700900</v>
+      </c>
+      <c r="J66" s="3">
+        <v>5398100</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
@@ -2446,25 +2446,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>5053800</v>
+        <v>5049600</v>
       </c>
       <c r="E72" s="3">
-        <v>5257100</v>
+        <v>5614300</v>
       </c>
       <c r="F72" s="3">
-        <v>5551800</v>
+        <v>6789800</v>
       </c>
       <c r="G72" s="3">
-        <v>5532000</v>
+        <v>7546800</v>
       </c>
       <c r="H72" s="3">
-        <v>4979100</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
+        <v>6448800</v>
+      </c>
+      <c r="I72" s="3">
+        <v>6106700</v>
+      </c>
+      <c r="J72" s="3">
+        <v>5636700</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
@@ -2566,25 +2566,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>6984000</v>
+        <v>6978200</v>
       </c>
       <c r="E76" s="3">
-        <v>6901600</v>
+        <v>7371200</v>
       </c>
       <c r="F76" s="3">
-        <v>6852500</v>
+        <v>8382400</v>
       </c>
       <c r="G76" s="3">
-        <v>6558200</v>
+        <v>8949800</v>
       </c>
       <c r="H76" s="3">
-        <v>6089600</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
+        <v>7892100</v>
+      </c>
+      <c r="I76" s="3">
+        <v>7495400</v>
+      </c>
+      <c r="J76" s="3">
+        <v>7159200</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
@@ -2648,8 +2648,8 @@
       <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2" t="s">
-        <v>3</v>
+      <c r="J80" s="2">
+        <v>43100</v>
       </c>
       <c r="K80" s="2" t="s">
         <v>3</v>
@@ -2661,25 +2661,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>311500</v>
+        <v>311200</v>
       </c>
       <c r="E81" s="3">
-        <v>610900</v>
+        <v>652400</v>
       </c>
       <c r="F81" s="3">
-        <v>778400</v>
+        <v>952200</v>
       </c>
       <c r="G81" s="3">
-        <v>895600</v>
+        <v>1222200</v>
       </c>
       <c r="H81" s="3">
-        <v>1052300</v>
+        <v>1363800</v>
       </c>
       <c r="I81" s="3">
-        <v>1091300</v>
-      </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
+        <v>1400900</v>
+      </c>
+      <c r="J81" s="3">
+        <v>1305200</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
@@ -2705,25 +2705,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>636100</v>
+        <v>635600</v>
       </c>
       <c r="E83" s="3">
-        <v>637100</v>
+        <v>680500</v>
       </c>
       <c r="F83" s="3">
-        <v>620100</v>
+        <v>758600</v>
       </c>
       <c r="G83" s="3">
-        <v>611200</v>
+        <v>834100</v>
       </c>
       <c r="H83" s="3">
-        <v>591900</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
+        <v>767100</v>
+      </c>
+      <c r="I83" s="3">
+        <v>552900</v>
+      </c>
+      <c r="J83" s="3">
+        <v>483900</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
@@ -2885,25 +2885,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1437600</v>
+        <v>1436400</v>
       </c>
       <c r="E89" s="3">
-        <v>929400</v>
+        <v>992700</v>
       </c>
       <c r="F89" s="3">
-        <v>1246200</v>
+        <v>1524500</v>
       </c>
       <c r="G89" s="3">
-        <v>1524500</v>
+        <v>2080500</v>
       </c>
       <c r="H89" s="3">
-        <v>1736100</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
+        <v>2250000</v>
+      </c>
+      <c r="I89" s="3">
+        <v>1782900</v>
+      </c>
+      <c r="J89" s="3">
+        <v>1650000</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
@@ -2929,25 +2929,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-384600</v>
+        <v>-384300</v>
       </c>
       <c r="E91" s="3">
-        <v>-465200</v>
+        <v>-496800</v>
       </c>
       <c r="F91" s="3">
-        <v>-425700</v>
+        <v>-520700</v>
       </c>
       <c r="G91" s="3">
-        <v>-421700</v>
+        <v>-575500</v>
       </c>
       <c r="H91" s="3">
-        <v>-596100</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J91" s="3" t="s">
-        <v>3</v>
+        <v>-772600</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-731900</v>
+      </c>
+      <c r="J91" s="3">
+        <v>-742800</v>
       </c>
       <c r="K91" s="3" t="s">
         <v>3</v>
@@ -3019,25 +3019,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-776000</v>
+        <v>-775400</v>
       </c>
       <c r="E94" s="3">
-        <v>-531900</v>
+        <v>-568100</v>
       </c>
       <c r="F94" s="3">
-        <v>-477300</v>
+        <v>-583900</v>
       </c>
       <c r="G94" s="3">
-        <v>-439800</v>
+        <v>-600200</v>
       </c>
       <c r="H94" s="3">
-        <v>-669300</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
+        <v>-867400</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-1439100</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-853600</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
@@ -3063,19 +3063,19 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-492300</v>
+        <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>-489400</v>
+        <v>0</v>
       </c>
       <c r="F96" s="3">
-        <v>-481800</v>
+        <v>0</v>
       </c>
       <c r="G96" s="3">
-        <v>-461400</v>
+        <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>-429600</v>
+        <v>0</v>
       </c>
       <c r="I96" s="3">
         <v>0</v>
@@ -3183,25 +3183,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-567900</v>
+        <v>-567400</v>
       </c>
       <c r="E100" s="3">
-        <v>-989100</v>
+        <v>-1056400</v>
       </c>
       <c r="F100" s="3">
-        <v>-1005200</v>
+        <v>-1229600</v>
       </c>
       <c r="G100" s="3">
-        <v>-618200</v>
+        <v>-843600</v>
       </c>
       <c r="H100" s="3">
-        <v>-895800</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
+        <v>-1160900</v>
+      </c>
+      <c r="I100" s="3">
+        <v>-989600</v>
+      </c>
+      <c r="J100" s="3">
+        <v>-472700</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
@@ -3213,25 +3213,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>72600</v>
+        <v>72500</v>
       </c>
       <c r="E101" s="3">
-        <v>110000</v>
+        <v>117500</v>
       </c>
       <c r="F101" s="3">
-        <v>114800</v>
+        <v>140500</v>
       </c>
       <c r="G101" s="3">
-        <v>-15700</v>
+        <v>-21500</v>
       </c>
       <c r="H101" s="3">
-        <v>-2800</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
+        <v>-3600</v>
+      </c>
+      <c r="I101" s="3">
+        <v>-56800</v>
+      </c>
+      <c r="J101" s="3">
+        <v>31900</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>3</v>
@@ -3243,25 +3243,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>166200</v>
+        <v>166100</v>
       </c>
       <c r="E102" s="3">
-        <v>-481500</v>
+        <v>-514300</v>
       </c>
       <c r="F102" s="3">
-        <v>-121500</v>
+        <v>-148600</v>
       </c>
       <c r="G102" s="3">
-        <v>450800</v>
+        <v>615200</v>
       </c>
       <c r="H102" s="3">
-        <v>168300</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
+        <v>218100</v>
+      </c>
+      <c r="I102" s="3">
+        <v>-702700</v>
+      </c>
+      <c r="J102" s="3">
+        <v>355600</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/KAOOY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/KAOOY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
   <si>
     <t>KAOOY</t>
   </si>
@@ -656,148 +656,160 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L7" s="2"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>10357800</v>
+      </c>
+      <c r="E8" s="3">
         <v>10872300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>11761800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>12322300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>13390500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>13823000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>13744800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>13223400</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L8" s="3"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>6297200</v>
+      </c>
+      <c r="E9" s="3">
         <v>6896600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>7603700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>7344000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>7667200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>7809600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>7783700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>7405400</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L9" s="3"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>4060600</v>
+      </c>
+      <c r="E10" s="3">
         <v>3975700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4158100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4978300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>5723400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>6013400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>5961100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>5818000</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -810,38 +822,42 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>394900</v>
+      </c>
+      <c r="E12" s="3">
         <v>443900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>459500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>512400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>566900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>544200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>525700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>503400</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -869,69 +885,78 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-      <c r="L13" s="3"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
         <v>285000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>27700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>80200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>32400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>40000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>57300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>33100</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L14" s="3"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>562400</v>
+      </c>
+      <c r="E15" s="3">
         <v>197400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>201000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>227400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>263700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>245900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>146300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>121200</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L15" s="3"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -941,68 +966,75 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>9425000</v>
+      </c>
+      <c r="E17" s="3">
         <v>10161400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>10899400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>10995700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>11657000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>11834800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>11794400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>11372100</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L17" s="3"/>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M17" s="3"/>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>932700</v>
+      </c>
+      <c r="E18" s="3">
         <v>710900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>862400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1326600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1733500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1988200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1950400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1851300</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L18" s="3"/>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1015,158 +1047,174 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-22100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-25300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-44800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-66200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-6200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-3000</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L20" s="3"/>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1517300</v>
+      </c>
+      <c r="E21" s="3">
         <v>933600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1108200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1620200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1996300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2240400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2095500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1975500</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L21" s="3"/>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" s="3"/>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>26000</v>
+      </c>
+      <c r="E22" s="3">
         <v>24000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>17900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>21600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>29900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>33700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>17600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>19200</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L22" s="3"/>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>960600</v>
+      </c>
+      <c r="E23" s="3">
         <v>452900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>878500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1302800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1685700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1938300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1889000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1813700</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L23" s="3"/>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M23" s="3"/>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>258600</v>
+      </c>
+      <c r="E24" s="3">
         <v>125500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>213100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>335100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>444800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>554800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>473200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>494400</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L24" s="3"/>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M24" s="3"/>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1194,69 +1242,78 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-      <c r="L25" s="3"/>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3"/>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>702000</v>
+      </c>
+      <c r="E26" s="3">
         <v>327400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>665400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>967700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1240900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1383400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1415800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1319400</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L26" s="3"/>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M26" s="3"/>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>685500</v>
+      </c>
+      <c r="E27" s="3">
         <v>311200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>652400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>952200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1222200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1363800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1400900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1305200</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L27" s="3"/>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M27" s="3"/>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1284,9 +1341,12 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-      <c r="L28" s="3"/>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3"/>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1311,12 +1371,15 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L29" s="3"/>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M29" s="3"/>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1344,9 +1407,12 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-      <c r="L30" s="3"/>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3"/>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1374,69 +1440,78 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-      <c r="L31" s="3"/>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3"/>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>22100</v>
+      </c>
+      <c r="E32" s="3">
         <v>25300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>44800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>66200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>6200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>3000</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L32" s="3"/>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M32" s="3"/>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>685500</v>
+      </c>
+      <c r="E33" s="3">
         <v>311200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>652400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>952200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1222200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1363800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1400900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1305200</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L33" s="3"/>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M33" s="3"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1464,74 +1539,83 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-      <c r="L34" s="3"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3"/>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>685500</v>
+      </c>
+      <c r="E35" s="3">
         <v>311200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>652400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>952200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1222200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1363800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1400900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1305200</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L35" s="3"/>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M35" s="3"/>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L38" s="2"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1544,8 +1628,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1558,38 +1643,42 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2275200</v>
+      </c>
+      <c r="E41" s="3">
         <v>2069100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2034100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2918800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3422000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2665500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2424300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3045900</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L41" s="3"/>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M41" s="3"/>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1614,222 +1703,246 @@
       <c r="J42" s="3">
         <v>0</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L42" s="3"/>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M42" s="3"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1549100</v>
+      </c>
+      <c r="E43" s="3">
         <v>1639600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1780300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1899600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1962500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1948900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2078600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2017800</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L43" s="3"/>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M43" s="3"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1746800</v>
+      </c>
+      <c r="E44" s="3">
         <v>1871500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2111000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1980800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1915000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1837300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1800800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1632900</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L44" s="3"/>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M44" s="3"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>242600</v>
+      </c>
+      <c r="E45" s="3">
         <v>136100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>112600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>150900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>166100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>251100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>229400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>226700</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L45" s="3"/>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5813700</v>
+      </c>
+      <c r="E46" s="3">
         <v>5796700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6121100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7033200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>7542100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6781800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6620000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>7008300</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L46" s="3"/>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M46" s="3"/>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>92400</v>
+      </c>
+      <c r="E47" s="3">
         <v>352300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>343600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>382700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>379800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>367000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>362300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>405900</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L47" s="3"/>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3"/>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3434000</v>
+      </c>
+      <c r="E48" s="3">
         <v>3879200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4382700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4973700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5624200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5536200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3818400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3514000</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L48" s="3"/>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M48" s="3"/>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1974000</v>
+      </c>
+      <c r="E49" s="3">
         <v>2132800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1911300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2050900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2182900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2093100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2067500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1381100</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L49" s="3"/>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M49" s="3"/>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1857,9 +1970,12 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-      <c r="L50" s="3"/>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3"/>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1887,14 +2003,17 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-      <c r="L51" s="3"/>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3"/>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>3</v>
+      <c r="D52" s="3">
+        <v>250600</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>3</v>
@@ -1917,9 +2036,12 @@
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L52" s="3"/>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M52" s="3"/>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1947,39 +2069,45 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-      <c r="L53" s="3"/>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3"/>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>11876600</v>
+      </c>
+      <c r="E54" s="3">
         <v>12554800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>13091000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>14799700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>16138600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>15218700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>13316200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>12672600</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L54" s="3"/>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M54" s="3"/>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1992,8 +2120,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2006,188 +2135,207 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1641200</v>
+      </c>
+      <c r="E57" s="3">
         <v>1670800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1848500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1989700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2091400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2045600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2055900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1996700</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L57" s="3"/>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M57" s="3"/>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>355500</v>
+      </c>
+      <c r="E58" s="3">
         <v>234500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>645400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>226600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>486900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>415500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>375100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>231000</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L58" s="3"/>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M58" s="3"/>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1244600</v>
+      </c>
+      <c r="E59" s="3">
         <v>755800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>526300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>696500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>759700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>778000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>717600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>725200</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L59" s="3"/>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3"/>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3241300</v>
+      </c>
+      <c r="E60" s="3">
         <v>3262800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3690100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3664300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4121900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3979900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3926900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3743700</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L60" s="3"/>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M60" s="3"/>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1204900</v>
+      </c>
+      <c r="E61" s="3">
         <v>1617500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1348100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2107000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2169900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2236700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>748300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>867800</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
-      <c r="L61" s="3"/>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3"/>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>128200</v>
+      </c>
+      <c r="E62" s="3">
         <v>146300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>159000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>173400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>209500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>207700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>229000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>208300</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L62" s="3"/>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3"/>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2215,9 +2363,12 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-      <c r="L63" s="3"/>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3"/>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2245,9 +2396,12 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-      <c r="L64" s="3"/>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3"/>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2275,39 +2429,45 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-      <c r="L65" s="3"/>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3"/>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4887400</v>
+      </c>
+      <c r="E66" s="3">
         <v>5375200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5543000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6254500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7048200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>7200200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5700900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5398100</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L66" s="3"/>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M66" s="3"/>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2320,8 +2480,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2349,9 +2510,12 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-      <c r="L68" s="3"/>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3"/>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2379,9 +2543,12 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-      <c r="L69" s="3"/>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3"/>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2409,9 +2576,12 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-      <c r="L70" s="3"/>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3"/>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2439,39 +2609,45 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-      <c r="L71" s="3"/>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3"/>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4762600</v>
+      </c>
+      <c r="E72" s="3">
         <v>5049600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>5614300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>6789800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>7546800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>6448800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>6106700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>5636700</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L72" s="3"/>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M72" s="3"/>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2499,9 +2675,12 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-      <c r="L73" s="3"/>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3"/>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2529,9 +2708,12 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-      <c r="L74" s="3"/>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3"/>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2559,39 +2741,45 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-      <c r="L75" s="3"/>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3"/>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6785200</v>
+      </c>
+      <c r="E76" s="3">
         <v>6978200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7371200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8382400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8949800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7892100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7495400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7159200</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L76" s="3"/>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M76" s="3"/>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2619,74 +2807,83 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-      <c r="L77" s="3"/>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3"/>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L80" s="2"/>
-    </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M80" s="2"/>
+    </row>
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>685500</v>
+      </c>
+      <c r="E81" s="3">
         <v>311200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>652400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>952200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1222200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1363800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1400900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1305200</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L81" s="3"/>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M81" s="3"/>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2699,38 +2896,42 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>488400</v>
+      </c>
+      <c r="E83" s="3">
         <v>635600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>680500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>758600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>834100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>767100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>552900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>483900</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L83" s="3"/>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M83" s="3"/>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2758,9 +2959,12 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-      <c r="L84" s="3"/>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3"/>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2788,9 +2992,12 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-      <c r="L85" s="3"/>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3"/>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2818,9 +3025,12 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-      <c r="L86" s="3"/>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3"/>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2848,9 +3058,12 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-      <c r="L87" s="3"/>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3"/>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2878,39 +3091,45 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-      <c r="L88" s="3"/>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3"/>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1282200</v>
+      </c>
+      <c r="E89" s="3">
         <v>1436400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>992700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1524500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2080500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2250000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1782900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1650000</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L89" s="3"/>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M89" s="3"/>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2923,38 +3142,42 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-365100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-384300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-496800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-520700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-575500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-772600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-731900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-742800</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L91" s="3"/>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M91" s="3"/>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2982,9 +3205,12 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-      <c r="L92" s="3"/>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3"/>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3012,39 +3238,45 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-      <c r="L93" s="3"/>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3"/>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-292000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-775400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-568100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-583900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-600200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-867400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1439100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-853600</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L94" s="3"/>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M94" s="3"/>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3057,13 +3289,14 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>446800</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>
@@ -3086,9 +3319,12 @@
       <c r="K96" s="3">
         <v>0</v>
       </c>
-      <c r="L96" s="3"/>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3"/>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3116,9 +3352,12 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-      <c r="L97" s="3"/>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3"/>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3146,9 +3385,12 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-      <c r="L98" s="3"/>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3"/>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3176,97 +3418,109 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-      <c r="L99" s="3"/>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3"/>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-665200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-567400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1056400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1229600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-843600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1160900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-989600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-472700</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L100" s="3"/>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M100" s="3"/>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>95100</v>
+      </c>
+      <c r="E101" s="3">
         <v>72500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>117500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>140500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-21500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-3600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-56800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>31900</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L101" s="3"/>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M101" s="3"/>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>420100</v>
+      </c>
+      <c r="E102" s="3">
         <v>166100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-514300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-148600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>615200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>218100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-702700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>355600</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L102" s="3"/>
+      <c r="L102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/KAOOY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/KAOOY_YR_FIN.xlsx
@@ -894,8 +894,8 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>-10400</v>
       </c>
       <c r="E14" s="3">
         <v>285000</v>
@@ -928,7 +928,7 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>562400</v>
+        <v>180200</v>
       </c>
       <c r="E15" s="3">
         <v>197400</v>
@@ -973,7 +973,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>9425000</v>
+        <v>9435400</v>
       </c>
       <c r="E17" s="3">
         <v>10161400</v>
@@ -1006,7 +1006,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>932700</v>
+        <v>922400</v>
       </c>
       <c r="E18" s="3">
         <v>710900</v>
@@ -1054,7 +1054,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-22100</v>
+        <v>-20300</v>
       </c>
       <c r="E20" s="3">
         <v>-25300</v>
@@ -1087,7 +1087,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1517300</v>
+        <v>1122900</v>
       </c>
       <c r="E21" s="3">
         <v>933600</v>
@@ -1120,7 +1120,7 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>26000</v>
+        <v>23000</v>
       </c>
       <c r="E22" s="3">
         <v>24000</v>
@@ -1450,7 +1450,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>22100</v>
+        <v>20300</v>
       </c>
       <c r="E32" s="3">
         <v>25300</v>
@@ -1782,7 +1782,7 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>242600</v>
+        <v>155100</v>
       </c>
       <c r="E45" s="3">
         <v>136100</v>
@@ -1848,7 +1848,7 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>92400</v>
+        <v>343000</v>
       </c>
       <c r="E47" s="3">
         <v>352300</v>
@@ -2012,8 +2012,8 @@
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>250600</v>
+      <c r="D52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>3</v>
@@ -2208,7 +2208,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1244600</v>
+        <v>640300</v>
       </c>
       <c r="E59" s="3">
         <v>755800</v>
@@ -2903,7 +2903,7 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>488400</v>
+        <v>562400</v>
       </c>
       <c r="E83" s="3">
         <v>635600</v>
@@ -3296,7 +3296,7 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>446800</v>
+        <v>0</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>

--- a/AAII_Financials/Yearly/KAOOY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/KAOOY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="92">
   <si>
     <t>KAOOY</t>
   </si>
@@ -656,160 +656,172 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N7" s="2"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>10770200</v>
+      </c>
+      <c r="E8" s="3">
         <v>10357800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>10872300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>11761800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>12322300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>13390500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>13823000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>13744800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>13223400</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M8" s="3"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>6508600</v>
+      </c>
+      <c r="E9" s="3">
         <v>6297200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>6896600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>7603700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>7344000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>7667200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>7809600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>7783700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>7405400</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M9" s="3"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>4261600</v>
+      </c>
+      <c r="E10" s="3">
         <v>4060600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3975700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4158100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>4978300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>5723400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>6013400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>5961100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>5818000</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M10" s="3"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -823,41 +835,45 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>389900</v>
+      </c>
+      <c r="E12" s="3">
         <v>394900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>443900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>459500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>512400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>566900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>544200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>525700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>503400</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M12" s="3"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N12" s="3"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -888,75 +904,84 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-      <c r="M13" s="3"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-10400</v>
+        <v>28200</v>
       </c>
       <c r="E14" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F14" s="3">
         <v>285000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>27700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>80200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>32400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>40000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>57300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>33100</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M14" s="3"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>180200</v>
+        <v>364800</v>
       </c>
       <c r="E15" s="3">
+        <v>379400</v>
+      </c>
+      <c r="F15" s="3">
         <v>197400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>201000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>227400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>263700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>245900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>146300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>121200</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M15" s="3"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N15" s="3"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -967,74 +992,81 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>9435400</v>
+        <v>9699900</v>
       </c>
       <c r="E17" s="3">
+        <v>9430000</v>
+      </c>
+      <c r="F17" s="3">
         <v>10161400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>10899400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>10995700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>11657000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>11834800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>11794400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>11372100</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M17" s="3"/>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N17" s="3"/>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>922400</v>
+        <v>1070200</v>
       </c>
       <c r="E18" s="3">
+        <v>927800</v>
+      </c>
+      <c r="F18" s="3">
         <v>710900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>862400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1326600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1733500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1988200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1950400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1851300</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M18" s="3"/>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" s="3"/>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1048,173 +1080,189 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-36200</v>
+      </c>
+      <c r="E20" s="3">
         <v>-20300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-25300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-44800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-66200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-6200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-3000</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M20" s="3"/>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="3"/>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1122900</v>
+        <v>1471300</v>
       </c>
       <c r="E21" s="3">
+        <v>1327500</v>
+      </c>
+      <c r="F21" s="3">
         <v>933600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1108200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1620200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1996300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2240400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2095500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1975500</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M21" s="3"/>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3"/>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>23000</v>
+        <v>17300</v>
       </c>
       <c r="E22" s="3">
+        <v>17400</v>
+      </c>
+      <c r="F22" s="3">
         <v>24000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>17900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>21600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>29900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>33700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>17600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>19200</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M22" s="3"/>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N22" s="3"/>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1083300</v>
+      </c>
+      <c r="E23" s="3">
         <v>960600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>452900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>878500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1302800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1685700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1938300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1889000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1813700</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M23" s="3"/>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N23" s="3"/>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>314200</v>
+      </c>
+      <c r="E24" s="3">
         <v>258600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>125500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>213100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>335100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>444800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>554800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>473200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>494400</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M24" s="3"/>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N24" s="3"/>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1245,75 +1293,84 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-      <c r="M25" s="3"/>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3"/>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>769100</v>
+      </c>
+      <c r="E26" s="3">
         <v>702000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>327400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>665400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>967700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1240900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1383400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1415800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1319400</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M26" s="3"/>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N26" s="3"/>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>765900</v>
+      </c>
+      <c r="E27" s="3">
         <v>685500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>311200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>652400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>952200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1222200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1363800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1400900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1305200</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M27" s="3"/>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N27" s="3"/>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1344,9 +1401,12 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-      <c r="M28" s="3"/>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3"/>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1374,12 +1434,15 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M29" s="3"/>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N29" s="3"/>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1410,9 +1473,12 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-      <c r="M30" s="3"/>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3"/>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1443,75 +1509,84 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-      <c r="M31" s="3"/>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3"/>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>36200</v>
+      </c>
+      <c r="E32" s="3">
         <v>20300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>25300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>44800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>66200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>6200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>3000</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M32" s="3"/>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="3"/>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>765900</v>
+      </c>
+      <c r="E33" s="3">
         <v>685500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>311200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>652400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>952200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1222200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1363800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1400900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1305200</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M33" s="3"/>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N33" s="3"/>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1542,80 +1617,89 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-      <c r="M34" s="3"/>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3"/>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>765900</v>
+      </c>
+      <c r="E35" s="3">
         <v>685500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>311200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>652400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>952200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1222200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1363800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1400900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1305200</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M35" s="3"/>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N35" s="3"/>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M38" s="2"/>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N38" s="2"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1629,8 +1713,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1644,41 +1729,45 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2061900</v>
+      </c>
+      <c r="E41" s="3">
         <v>2275200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2069100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2034100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2918800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3422000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2665500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2424300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3045900</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M41" s="3"/>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N41" s="3"/>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1706,243 +1795,267 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M42" s="3"/>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N42" s="3"/>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1599300</v>
+      </c>
+      <c r="E43" s="3">
         <v>1549100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1639600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1780300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1899600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1962500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1948900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2078600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2017800</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M43" s="3"/>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N43" s="3"/>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1864700</v>
+      </c>
+      <c r="E44" s="3">
         <v>1746800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1871500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2111000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1980800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1915000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1837300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1800800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1632900</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M44" s="3"/>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N44" s="3"/>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>163800</v>
+      </c>
+      <c r="E45" s="3">
         <v>155100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>136100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>112600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>150900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>166100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>251100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>229400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>226700</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M45" s="3"/>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3"/>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5777800</v>
+      </c>
+      <c r="E46" s="3">
         <v>5813700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5796700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6121100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>7033200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7542100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6781800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6620000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>7008300</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M46" s="3"/>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N46" s="3"/>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>343000</v>
+        <v>99600</v>
       </c>
       <c r="E47" s="3">
+        <v>92400</v>
+      </c>
+      <c r="F47" s="3">
         <v>352300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>343600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>382700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>379800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>367000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>362300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>405900</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M47" s="3"/>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N47" s="3"/>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3548100</v>
+      </c>
+      <c r="E48" s="3">
         <v>3434000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3879200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4382700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4973700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5624200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5536200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3818400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3514000</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M48" s="3"/>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N48" s="3"/>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1980600</v>
+      </c>
+      <c r="E49" s="3">
         <v>1974000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2132800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1911300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2050900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2182900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2093100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2067500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1381100</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M49" s="3"/>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N49" s="3"/>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1973,9 +2086,12 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-      <c r="M50" s="3"/>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3"/>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2006,17 +2122,20 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-      <c r="M51" s="3"/>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3"/>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>3</v>
+      <c r="D52" s="3">
+        <v>276800</v>
+      </c>
+      <c r="E52" s="3">
+        <v>250600</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>3</v>
@@ -2039,9 +2158,12 @@
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M52" s="3"/>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N52" s="3"/>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2072,42 +2194,48 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-      <c r="M53" s="3"/>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3"/>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>11959200</v>
+      </c>
+      <c r="E54" s="3">
         <v>11876600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>12554800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>13091000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>14799700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>16138600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>15218700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>13316200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>12672600</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M54" s="3"/>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N54" s="3"/>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2121,8 +2249,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2136,206 +2265,225 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1641200</v>
+        <v>1103400</v>
       </c>
       <c r="E57" s="3">
+        <v>1099800</v>
+      </c>
+      <c r="F57" s="3">
         <v>1670800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1848500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1989700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2091400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2045600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2055900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1996700</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M57" s="3"/>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N57" s="3"/>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>299400</v>
+      </c>
+      <c r="E58" s="3">
         <v>355500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>234500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>645400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>226600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>486900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>415500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>375100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>231000</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M58" s="3"/>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N58" s="3"/>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>640300</v>
+        <v>1243700</v>
       </c>
       <c r="E59" s="3">
+        <v>1103600</v>
+      </c>
+      <c r="F59" s="3">
         <v>755800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>526300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>696500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>759700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>778000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>717600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>725200</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M59" s="3"/>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3"/>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3305100</v>
+      </c>
+      <c r="E60" s="3">
         <v>3241300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3262800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3690100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3664300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4121900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3979900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3926900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3743700</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M60" s="3"/>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N60" s="3"/>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1251400</v>
+      </c>
+      <c r="E61" s="3">
         <v>1204900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1617500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1348100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2107000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2169900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2236700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>748300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>867800</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
-      <c r="M61" s="3"/>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3"/>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>117600</v>
+      </c>
+      <c r="E62" s="3">
         <v>128200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>146300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>159000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>173400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>209500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>207700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>229000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>208300</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M62" s="3"/>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3"/>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2366,9 +2514,12 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-      <c r="M63" s="3"/>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3"/>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2399,9 +2550,12 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-      <c r="M64" s="3"/>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3"/>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2432,42 +2586,48 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-      <c r="M65" s="3"/>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3"/>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4977100</v>
+      </c>
+      <c r="E66" s="3">
         <v>4887400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5375200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5543000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6254500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>7048200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>7200200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5700900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5398100</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M66" s="3"/>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N66" s="3"/>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2481,8 +2641,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2513,9 +2674,12 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-      <c r="M68" s="3"/>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3"/>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2546,9 +2710,12 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-      <c r="M69" s="3"/>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3"/>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2579,9 +2746,12 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-      <c r="M70" s="3"/>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3"/>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2612,42 +2782,48 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-      <c r="M71" s="3"/>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3"/>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4570600</v>
+      </c>
+      <c r="E72" s="3">
         <v>4762600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>5049600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>5614300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>6789800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>7546800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>6448800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>6106700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>5636700</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M72" s="3"/>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N72" s="3"/>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2678,9 +2854,12 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-      <c r="M73" s="3"/>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3"/>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2711,9 +2890,12 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-      <c r="M74" s="3"/>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3"/>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2744,42 +2926,48 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-      <c r="M75" s="3"/>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3"/>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6786700</v>
+      </c>
+      <c r="E76" s="3">
         <v>6785200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6978200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>7371200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8382400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8949800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7892100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7495400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7159200</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M76" s="3"/>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N76" s="3"/>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2810,80 +2998,89 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-      <c r="M77" s="3"/>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3"/>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M80" s="2"/>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N80" s="2"/>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>765900</v>
+      </c>
+      <c r="E81" s="3">
         <v>685500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>311200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>652400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>952200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1222200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1363800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1400900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1305200</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M81" s="3"/>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N81" s="3"/>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2897,41 +3094,45 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>562400</v>
+        <v>468800</v>
       </c>
       <c r="E83" s="3">
+        <v>484900</v>
+      </c>
+      <c r="F83" s="3">
         <v>635600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>680500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>758600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>834100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>767100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>552900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>483900</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M83" s="3"/>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N83" s="3"/>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2962,9 +3163,12 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-      <c r="M84" s="3"/>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3"/>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2995,9 +3199,12 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-      <c r="M85" s="3"/>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3"/>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3028,9 +3235,12 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-      <c r="M86" s="3"/>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3"/>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3061,9 +3271,12 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-      <c r="M87" s="3"/>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3"/>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3094,42 +3307,48 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-      <c r="M88" s="3"/>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3"/>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1273600</v>
+      </c>
+      <c r="E89" s="3">
         <v>1282200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1436400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>992700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1524500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2080500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2250000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1782900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1650000</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M89" s="3"/>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N89" s="3"/>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3143,41 +3362,45 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-390400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-365100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-384300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-496800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-520700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-575500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-772600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-731900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-742800</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M91" s="3"/>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N91" s="3"/>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3208,9 +3431,12 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-      <c r="M92" s="3"/>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3"/>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3241,42 +3467,48 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-      <c r="M93" s="3"/>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3"/>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-445000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-292000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-775400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-568100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-583900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-600200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-867400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1439100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-853600</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M94" s="3"/>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3"/>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3290,41 +3522,45 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>453800</v>
+      </c>
+      <c r="E96" s="3">
         <v>446800</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>491900</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>522700</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>589400</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>629700</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>556800</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>518100</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
-      <c r="M96" s="3"/>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3"/>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3355,9 +3591,12 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-      <c r="M97" s="3"/>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3"/>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3388,9 +3627,12 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-      <c r="M98" s="3"/>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3"/>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3421,106 +3663,118 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-      <c r="M99" s="3"/>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3"/>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1117000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-665200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-567400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1056400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1229600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-843600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1160900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-989600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-472700</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M100" s="3"/>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3"/>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>68800</v>
+      </c>
+      <c r="E101" s="3">
         <v>95100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>72500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>117500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>140500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-21500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-3600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-56800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>31900</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M101" s="3"/>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N101" s="3"/>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-219600</v>
+      </c>
+      <c r="E102" s="3">
         <v>420100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>166100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-514300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-148600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>615200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>218100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-702700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>355600</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M102" s="3"/>
+      <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
